--- a/data/credit_bond_all_2026-10-22.xlsx
+++ b/data/credit_bond_all_2026-10-22.xlsx
@@ -8154,17 +8154,17 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26新五丰MTN001(乡村振兴)(取消发行)</t>
+          <t>26兖矿能源MTN003(并购)</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>10-22 18:00</t>
+          <t>10-23 18:00</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>DY102684184.IB</t>
+          <t>102684213.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -8173,90 +8173,116 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="F35" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>20.0</v>
+      </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
+          <t>1.40 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>40.76</v>
+      </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>26兖矿能源MTN002A(并购)</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>2.81Y+N</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>1.6429</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>兖矿能源集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>B- 40.60</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>10-22 10:00</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>湖南新五丰股份有限公司</t>
-        </is>
-      </c>
-      <c r="P35" s="3"/>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t>10-22 09:00</t>
-        </is>
-      </c>
-      <c r="S35" s="3" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="U35" s="3"/>
-      <c r="V35" s="3"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="U35" s="4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="V35" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>2.05%~2.15%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z35" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>山东省-济宁市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具发行金额为人民币7亿元。募集资金全部用于归还发行人存量有息负债,全部用于乡村振兴用途</t>
+          <t>本期中期票据发行规模上限25亿元,拟用于置换发行人一年内归还并购贷款的自有资金</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,兴业银行股份有限公司</t>
+          <t>兴业银行股份有限公司,招商银行股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
@@ -8277,7 +8303,7 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>湖南新五丰股份有限公司2026年度第一期中期票据(乡村振兴)(取消发行)</t>
+          <t>兖矿能源集团股份有限公司2026年度第三期中期票据(并购)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8287,145 +8313,153 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2029-10-23</t>
+          <t>2029-10-26</t>
         </is>
       </c>
       <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="AM35" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="AN35" s="3" t="inlineStr">
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>其他煤炭</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AX35" s="3" t="inlineStr">
+        <is>
+          <t>次级债权</t>
+        </is>
+      </c>
+      <c r="AY35" s="3" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="AO35" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP35" s="3"/>
-      <c r="AQ35" s="3" t="inlineStr">
-        <is>
-          <t>农林牧渔</t>
-        </is>
-      </c>
-      <c r="AR35" s="3" t="inlineStr">
-        <is>
-          <t>畜牧业</t>
-        </is>
-      </c>
-      <c r="AS35" s="3" t="inlineStr">
-        <is>
-          <t>禽畜养殖</t>
-        </is>
-      </c>
-      <c r="AT35" s="3" t="inlineStr">
-        <is>
-          <t>畜禽养殖</t>
-        </is>
-      </c>
-      <c r="AU35" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV35" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW35" s="3" t="inlineStr">
-        <is>
-          <t>含权</t>
-        </is>
-      </c>
-      <c r="AX35" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY35" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="AZ35" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ35" s="3"/>
     </row>
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26中远海特MTN001B(取消发行)</t>
+          <t>26东国03</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>10-22 18:00</t>
+          <t>10-22 19:00</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>DY102684207.IB</t>
+          <t>284343.SH</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>15Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F36" s="3"/>
+        <v>14.7</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>14.7</v>
+      </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>36.33</v>
+      </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>25山东海运MTN001</t>
+          <t>26东国02</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>1.55Y</t>
+          <t>2.98Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.7036</t>
+          <t>1.6596</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>1.6900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>中远海运特种运输股份有限公司</t>
+          <t>北京市东城区国有资本运营有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>D- 3.00</t>
+          <t>C+ 34.75</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8435,7 +8469,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>10-22 09:00</t>
+          <t>10-22 15:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8448,14 +8482,20 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="U36" s="3"/>
+      <c r="U36" s="4" t="n">
+        <v>3.5238</v>
+      </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X36" s="3"/>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>1.68%~1.78%</t>
+        </is>
+      </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -8464,54 +8504,54 @@
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>北京市-东城区</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>发行人本期拟发行的15亿元中期票据,募集资金用于发行人及其子公司偿还有息债务及用于支付造船款、补充日常流动性等相关生产经营活动。</t>
+          <t>本期债券募集资金扣除发行费用后，全部用于偿还公司有息负债</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国银行股份有限公司</t>
+          <t>浙商证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中邮证券有限责任公司,国新证券股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>中远海运特种运输股份有限公司2026年度第一期中期票据(品种二)(取消发行)</t>
+          <t>北京市东城区国有资本运营有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2041-10-23</t>
+          <t>2029-10-23</t>
         </is>
       </c>
       <c r="AK36" s="3"/>
       <c r="AL36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AM36" s="3" t="inlineStr">
@@ -8526,32 +8566,32 @@
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>航运</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>航运</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>航运</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8584,7 +8624,7 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26邮政CP005</t>
+          <t>26新五丰MTN001(乡村振兴)(取消发行)</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8594,66 +8634,48 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>042680352.IB</t>
+          <t>DY102684184.IB</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>0.93Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>50.0</v>
-      </c>
+        <v>7.0</v>
+      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.26 ~ 1.46</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>19.23</v>
-      </c>
+          <t>2.00 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>24邮政MTN010</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>337D</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.4565</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>1.4800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>中国邮政集团有限公司</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="inlineStr">
-        <is>
-          <t>A 76.80</t>
-        </is>
-      </c>
+          <t>湖南新五丰股份有限公司</t>
+        </is>
+      </c>
+      <c r="P37" s="3"/>
       <c r="Q37" s="3" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -8666,7 +8688,7 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
@@ -8678,44 +8700,44 @@
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.44%~1.48%</t>
+          <t>2.05%~2.15%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期短期融资券发行金额为50亿元,全部用于补充营运资金及偿还有息负债</t>
+          <t>发行人本期债务融资工具发行金额为人民币7亿元。募集资金全部用于归还发行人存量有息负债,全部用于乡村振兴用途</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,中国邮政储蓄银行股份有限公司,兴业银行股份有限公司,中信银行股份有限公司</t>
+          <t>中信银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG37" s="3" t="inlineStr">
@@ -8725,7 +8747,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>中国邮政集团有限公司2026年度第五期短期融资券</t>
+          <t>湖南新五丰股份有限公司2026年度第一期中期票据(乡村振兴)(取消发行)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8735,7 +8757,7 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2027-09-28</t>
+          <t>2029-10-23</t>
         </is>
       </c>
       <c r="AK37" s="3"/>
@@ -8746,7 +8768,7 @@
       </c>
       <c r="AM37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AN37" s="3" t="inlineStr">
@@ -8756,32 +8778,28 @@
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP37" s="3"/>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>农林牧渔</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>畜牧业</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>禽畜养殖</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>物流</t>
+          <t>畜禽养殖</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8796,7 +8814,7 @@
       </c>
       <c r="AW37" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX37" s="3" t="inlineStr">
@@ -8809,12 +8827,14 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="AZ37" s="3"/>
+      <c r="AZ37" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26锡公用MTN001</t>
+          <t>26中远海特MTN001B(取消发行)</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8824,64 +8844,58 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>102684192.IB</t>
+          <t>DY102684207.IB</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>15Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>8.5</v>
-      </c>
+        <v>7.5</v>
+      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>42.68</v>
-      </c>
+          <t>1.90 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>24锡公Y2</t>
+          <t>25山东海运MTN001</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>3.15Y+N</t>
+          <t>1.55Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.6602</t>
+          <t>1.7036</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6900/--</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>无锡市市政公用产业集团有限公司</t>
+          <t>中远海运特种运输股份有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>D+ 9.23</t>
+          <t>D- 3.00</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8896,7 +8910,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
@@ -8904,22 +8918,14 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="U38" s="4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="U38" s="3"/>
+      <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X38" s="3" t="inlineStr">
-        <is>
-          <t>1.72%~1.82%</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X38" s="3"/>
       <c r="Y38" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -8928,17 +8934,17 @@
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>发行人本期拟发行8.50亿元,募集资金拟用于偿还到期的永续中期票据[23锡公用MTN001]</t>
+          <t>发行人本期拟发行的15亿元中期票据,募集资金用于发行人及其子公司偿还有息债务及用于支付造船款、补充日常流动性等相关生产经营活动。</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中信银行股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
@@ -8949,7 +8955,7 @@
       </c>
       <c r="AF38" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG38" s="3" t="inlineStr">
@@ -8959,7 +8965,7 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>无锡市市政公用产业集团有限公司2026年度第一期中期票据</t>
+          <t>中远海运特种运输股份有限公司2026年度第一期中期票据(品种二)(取消发行)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -8969,7 +8975,7 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2031-10-23</t>
+          <t>2041-10-23</t>
         </is>
       </c>
       <c r="AK38" s="3"/>
@@ -8990,32 +8996,32 @@
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -9030,7 +9036,7 @@
       </c>
       <c r="AW38" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX38" s="3" t="inlineStr">
@@ -9043,14 +9049,12 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="AZ38" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ38" s="3"/>
     </row>
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26黄山供销SCP002</t>
+          <t>26邮政CP005</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -9060,64 +9064,64 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>012682515.IB</t>
+          <t>042680352.IB</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>0.33Y</t>
+          <t>0.93Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>2.0</v>
+        <v>50.0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>2.0</v>
+        <v>50.0</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.49 ~ 1.90</t>
+          <t>1.26 ~ 1.46</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>32.85</v>
+        <v>19.23</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26黄山供销MTN001</t>
+          <t>24邮政MTN010</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>2.79Y</t>
+          <t>337D</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.7818</t>
+          <t>1.4565</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>--/1.7800</t>
+          <t>1.4800/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>中国邮政集团有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 19.45</t>
+          <t>A 76.80</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9132,7 +9136,7 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
@@ -9141,51 +9145,49 @@
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V39" s="4" t="n">
-        <v>1.6</v>
-      </c>
+        <v>1.352</v>
+      </c>
+      <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.44%~1.48%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>安徽省-黄山市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>发行人本次拟发行2亿元超短期融资券,用于偿还发行人本部有息负债</t>
+          <t>本期短期融资券发行金额为50亿元,全部用于补充营运资金及偿还有息负债</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>交通银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,中国邮政储蓄银行股份有限公司,兴业银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG39" s="3" t="inlineStr">
@@ -9195,7 +9197,7 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司2026年度第二期超短期融资券</t>
+          <t>中国邮政集团有限公司2026年度第五期短期融资券</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -9205,14 +9207,10 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
-        </is>
-      </c>
-      <c r="AK39" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-09-28</t>
+        </is>
+      </c>
+      <c r="AK39" s="3"/>
       <c r="AL39" s="3" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -9230,32 +9228,32 @@
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>轻工制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>其他轻工制造</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>其他轻工制造</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>一般零售</t>
+          <t>物流</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -9288,59 +9286,59 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26云港Y2</t>
+          <t>26锡公用MTN001</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>10-22 19:00</t>
+          <t>10-22 18:00</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>284251.SH</t>
+          <t>102684192.IB</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>7+N</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>5.0</v>
+        <v>8.5</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>84.38</v>
+        <v>42.68</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>25云港Y4</t>
+          <t>24锡公Y2</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>3.89Y+N</t>
+          <t>3.15Y+N</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.9177</t>
+          <t>1.6602</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -9350,12 +9348,12 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>连云港港口集团有限公司</t>
+          <t>无锡市市政公用产业集团有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C- 19.98</t>
+          <t>D+ 9.23</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9365,12 +9363,12 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>10-22 15:00</t>
+          <t>10-22 09:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
@@ -9379,44 +9377,46 @@
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="V40" s="3"/>
+        <v>4.6</v>
+      </c>
+      <c r="V40" s="4" t="n">
+        <v>1.3</v>
+      </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>2.14%~2.24%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>江苏省-连云港市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后，拟将5亿元全部用于偿还到期的公司债券本金【23 云港Y3】</t>
+          <t>发行人本期拟发行8.50亿元,募集资金拟用于偿还到期的永续中期票据[23锡公用MTN001]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,中信证券股份有限公司,国泰海通证券股份有限公司,东吴证券股份有限公司</t>
+          <t>中信银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
@@ -9426,32 +9426,28 @@
       </c>
       <c r="AG40" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>连云港港口集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种二)</t>
+          <t>无锡市市政公用产业集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2033-10-23</t>
-        </is>
-      </c>
-      <c r="AK40" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-23</t>
+        </is>
+      </c>
+      <c r="AK40" s="3"/>
       <c r="AL40" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AM40" s="3" t="inlineStr">
@@ -9466,32 +9462,32 @@
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -9519,79 +9515,81 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="AZ40" s="3"/>
+      <c r="AZ40" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26粤海K2</t>
+          <t>26黄山供销SCP002</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>10-22 19:00</t>
+          <t>10-22 18:00</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>525061.SZ</t>
+          <t>012682515.IB</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>0.33Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.80</t>
+          <t>1.49 ~ 1.90</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>13.4</v>
+        <v>32.85</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>26粤海MTN002</t>
+          <t>26黄山供销MTN001</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>1.92Y</t>
+          <t>2.79Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.5180</t>
+          <t>1.7818</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>1.5300/1.5000</t>
+          <t>--/1.7800</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>广东粤海控股集团有限公司</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.04</t>
+          <t>C- 19.45</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9601,73 +9599,75 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>10-22 16:00</t>
+          <t>10-22 09:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="U41" s="4" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="V41" s="3"/>
+        <v>3.15</v>
+      </c>
+      <c r="V41" s="4" t="n">
+        <v>1.6</v>
+      </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.58%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>安徽省-黄山市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过10亿元(含)，本期债券的募集资金扣除发行费用后拟全部用于偿还到期有息债务</t>
+          <t>发行人本次拟发行2亿元超短期融资券,用于偿还发行人本部有息负债</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,兴业证券股份有限公司</t>
+          <t>交通银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF41" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG41" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>广东粤海控股集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)</t>
+          <t>黄山供销集团有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
@@ -9677,13 +9677,17 @@
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
-        </is>
-      </c>
-      <c r="AK41" s="3"/>
+          <t>2027-02-20</t>
+        </is>
+      </c>
+      <c r="AK41" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL41" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AM41" s="3" t="inlineStr">
@@ -9693,37 +9697,37 @@
       </c>
       <c r="AN41" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP41" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>轻工制造</t>
         </is>
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>其他轻工制造</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>其他轻工制造</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>一般零售</t>
         </is>
       </c>
       <c r="AU41" s="3" t="inlineStr">
@@ -9756,7 +9760,7 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26穗发01</t>
+          <t>26粤海K2</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -9766,12 +9770,12 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>246299.SH</t>
+          <t>525061.SZ</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
@@ -9782,48 +9786,48 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.20 ~ 1.80</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1.66</v>
+        <v>1.38</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>30.68</v>
+        <v>13.4</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>26广州发展MTN001</t>
+          <t>26粤海MTN002</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>4.59Y</t>
+          <t>1.92Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.6533</t>
+          <t>1.5180</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>1.6700/--</t>
+          <t>1.5300/1.5000</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>广州发展集团股份有限公司</t>
+          <t>广东粤海控股集团有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C- 20.00</t>
+          <t>C+ 34.04</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9833,7 +9837,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>10-22 15:00</t>
+          <t>10-22 16:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -9847,7 +9851,7 @@
         </is>
       </c>
       <c r="U42" s="4" t="n">
-        <v>4.73</v>
+        <v>5.03</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
@@ -9857,7 +9861,7 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.48%~1.58%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
@@ -9865,24 +9869,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z42" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>广东省</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过10亿元,拟全部用于偿还公司有息债务。[26广州发展SCP002]</t>
+          <t>本期债券发行规模为不超过10亿元(含)，本期债券的募集资金扣除发行费用后拟全部用于偿还到期有息债务</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,华泰联合证券有限责任公司,国泰海通证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,兴业证券股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
@@ -9898,12 +9898,12 @@
       </c>
       <c r="AG42" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>广州发展集团股份有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>广东粤海控股集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
@@ -9913,14 +9913,10 @@
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2031-10-26</t>
-        </is>
-      </c>
-      <c r="AK42" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2028-10-26</t>
+        </is>
+      </c>
+      <c r="AK42" s="3"/>
       <c r="AL42" s="3" t="inlineStr">
         <is>
           <t/>
@@ -9938,12 +9934,12 @@
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
@@ -9953,17 +9949,17 @@
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU42" s="3" t="inlineStr">
@@ -9996,7 +9992,7 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26六横01</t>
+          <t>26穗发01</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -10006,62 +10002,64 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>284195.SH</t>
+          <t>246299.SH</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F43" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>48.33</v>
+        <v>30.68</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>24六横01</t>
+          <t>26广州发展MTN001</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>2.79Y</t>
+          <t>4.59Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.7936</t>
+          <t>1.6533</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>--/1.7000</t>
+          <t>1.6700/--</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>舟山市六横国有资产投资经营有限公司</t>
+          <t>广州发展集团股份有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C- 19.22</t>
+          <t>C- 20.00</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -10081,40 +10079,46 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="U43" s="3"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="U43" s="4" t="n">
+        <v>4.73</v>
+      </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z43" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>浙江省-舟山市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,全部用于偿还公司债券本金[23六横01]</t>
+          <t>本期债券发行规模不超过10亿元,拟全部用于偿还公司有息债务。[26广州发展SCP002]</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>财通证券股份有限公司</t>
+          <t>平安证券股份有限公司,华泰联合证券有限责任公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
@@ -10135,17 +10139,17 @@
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>舟山市六横国有资产投资经营有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>广州发展集团股份有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2029-10-28</t>
+          <t>2031-10-26</t>
         </is>
       </c>
       <c r="AK43" s="3" t="inlineStr">
@@ -10165,37 +10169,37 @@
       </c>
       <c r="AN43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
@@ -10228,7 +10232,7 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26龙投03</t>
+          <t>26六横01</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -10238,62 +10242,62 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>284344.SH</t>
+          <t>284195.SH</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>28.68</v>
+        <v>48.33</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>26龙投K1</t>
+          <t>24六横01</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>2.92Y+2.00Y</t>
+          <t>2.79Y</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.6957</t>
+          <t>1.7936</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>1.7400/1.6980</t>
+          <t>--/1.7000</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>龙岩市投资开发集团有限公司</t>
+          <t>舟山市六横国有资产投资经营有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>B 50.83</t>
+          <t>C- 19.22</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10313,40 +10317,40 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>福建省-龙岩市</t>
+          <t>浙江省-舟山市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券本金。[23龙投02]</t>
+          <t>本期公司债券募集资金扣除发行费用后,全部用于偿还公司债券本金[23六横01]</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司,中信证券股份有限公司,华福证券股份有限公司</t>
+          <t>财通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
@@ -10367,7 +10371,7 @@
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>龙岩市投资开发集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>舟山市六横国有资产投资经营有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -10377,10 +10381,14 @@
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2031-10-27</t>
-        </is>
-      </c>
-      <c r="AK44" s="3"/>
+          <t>2029-10-28</t>
+        </is>
+      </c>
+      <c r="AK44" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL44" s="3" t="inlineStr">
         <is>
           <t/>
@@ -10393,17 +10401,17 @@
       </c>
       <c r="AN44" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP44" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ44" s="3" t="inlineStr">
@@ -10428,7 +10436,7 @@
       </c>
       <c r="AU44" s="3" t="inlineStr">
         <is>
-          <t>2029-10-27</t>
+          <t/>
         </is>
       </c>
       <c r="AV44" s="3" t="inlineStr">
@@ -10438,7 +10446,7 @@
       </c>
       <c r="AW44" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX44" s="3" t="inlineStr">
@@ -10456,72 +10464,72 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26润通01</t>
+          <t>26龙投03</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>10-22 18:30</t>
+          <t>10-22 19:00</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>284329.SH</t>
+          <t>284344.SH</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>44.68</v>
+        <v>28.68</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>26富阳交通PPN002</t>
+          <t>26龙投K1</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>4.31Y</t>
+          <t>2.92Y+2.00Y</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.7529</t>
+          <t>1.6957</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7400/1.6980</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>杭州富春润通控股集团有限公司</t>
+          <t>龙岩市投资开发集团有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C- 16.46</t>
+          <t>B 50.83</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10548,12 +10556,12 @@
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -10564,17 +10572,17 @@
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>福建省-龙岩市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期债券计划募集资金不超过15.00亿元(含15.00亿元),扣除发行费用后拟将募集资金全部用于偿还到期的公司债券(21富交02)本金[21富交02]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券本金。[23龙投02]</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>财通证券股份有限公司</t>
+          <t>兴业证券股份有限公司,中信证券股份有限公司,华福证券股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
@@ -10595,7 +10603,7 @@
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>杭州富春润通控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>龙岩市投资开发集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
@@ -10631,32 +10639,32 @@
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-27</t>
         </is>
       </c>
       <c r="AV45" s="3" t="inlineStr">
@@ -10666,7 +10674,7 @@
       </c>
       <c r="AW45" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX45" s="3" t="inlineStr">
@@ -10684,17 +10692,17 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26青信13(取消发行)</t>
+          <t>26润通01</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>10-22 19:00</t>
+          <t>10-22 18:30</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>DY246259.SH</t>
+          <t>284329.SH</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -10703,102 +10711,106 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>44.68</v>
+      </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>26富阳交通PPN002</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>4.31Y</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>1.7529</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>杭州富春润通控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>C- 16.46</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>10-22 15:00</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>26青岛国信MTN008A</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>4.84Y</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>1.7532</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t>1.7500/1.7300</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>青岛国信发展(集团)有限责任公司</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t>C 26.09</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t>10-22 16:00</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本期债券为第五期发行,发行规模不超过10.00亿元(含10.00亿元)。本期债券募集资金拟全部用于置换已偿还到期公司债券本金的自有资金[21青信01]</t>
+          <t>本期债券计划募集资金不超过15.00亿元(含15.00亿元),扣除发行费用后拟将募集资金全部用于偿还到期的公司债券(21富交02)本金[21富交02]</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,光大证券股份有限公司,招商证券股份有限公司</t>
+          <t>财通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD46" s="3"/>
@@ -10819,24 +10831,20 @@
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>青岛国信发展(集团)有限责任公司2026年面向专业投资者公开发行公司债券(第七期)(品种一)(取消发行)</t>
+          <t>杭州富春润通控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2031-10-26</t>
-        </is>
-      </c>
-      <c r="AK46" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-27</t>
+        </is>
+      </c>
+      <c r="AK46" s="3"/>
       <c r="AL46" s="3" t="inlineStr">
         <is>
           <t/>
@@ -10849,37 +10857,37 @@
       </c>
       <c r="AN46" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP46" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ46" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AT46" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU46" s="3" t="inlineStr">
@@ -10912,7 +10920,7 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26青信14</t>
+          <t>26青信13(取消发行)</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10922,54 +10930,48 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>246260.SH</t>
+          <t>DY246259.SH</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F47" s="4" t="n">
-        <v>10.0</v>
-      </c>
+      <c r="F47" s="3"/>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I47" s="4" t="n">
-        <v>53.86</v>
-      </c>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>26青岛国信MTN009B</t>
+          <t>26青岛国信MTN008A</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>9.92Y</t>
+          <t>4.84Y</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>2.1828</t>
+          <t>1.7532</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>2.2000/2.1400</t>
+          <t>1.7500/1.7300</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
@@ -11011,7 +11013,7 @@
       </c>
       <c r="X47" s="3" t="inlineStr">
         <is>
-          <t>2.09%~2.19%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y47" s="3" t="inlineStr">
@@ -11027,7 +11029,7 @@
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟全部用于置换已偿还到期公司债券本金的自有资金，[21青信01]</t>
+          <t>本期债券为第五期发行,发行规模不超过10.00亿元(含10.00亿元)。本期债券募集资金拟全部用于置换已偿还到期公司债券本金的自有资金[21青信01]</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
@@ -11053,7 +11055,7 @@
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>青岛国信发展(集团)有限责任公司2026年面向专业投资者公开发行公司债券(第七期)(品种二)</t>
+          <t>青岛国信发展(集团)有限责任公司2026年面向专业投资者公开发行公司债券(第七期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
@@ -11063,7 +11065,7 @@
       </c>
       <c r="AJ47" s="3" t="inlineStr">
         <is>
-          <t>2036-10-26</t>
+          <t>2031-10-26</t>
         </is>
       </c>
       <c r="AK47" s="3" t="inlineStr">
@@ -11146,7 +11148,7 @@
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26宁证04</t>
+          <t>26青信14</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -11156,64 +11158,64 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>246287.SH</t>
+          <t>246260.SH</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.00</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>1.54</v>
+        <v>2.18</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>29.4</v>
+        <v>53.86</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>26宁证03</t>
+          <t>26青岛国信MTN009B</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>1.92Y</t>
+          <t>9.92Y</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1.5380</t>
+          <t>2.1828</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>1.5700/--</t>
+          <t>2.2000/2.1400</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>南京证券股份有限公司</t>
+          <t>青岛国信发展(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>B- 35.34</t>
+          <t>C 26.09</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -11223,7 +11225,7 @@
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>10-22 15:00</t>
+          <t>10-22 16:00</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
@@ -11236,18 +11238,16 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="U48" s="4" t="n">
-        <v>4.64</v>
-      </c>
+      <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X48" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.60%</t>
+          <t>2.09%~2.19%</t>
         </is>
       </c>
       <c r="Y48" s="3" t="inlineStr">
@@ -11255,30 +11255,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z48" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z48" s="3"/>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过20亿元(含20亿元),全部用于偿还到期公司债券本金。[25宁证08]</t>
+          <t>本期债券募集资金拟全部用于置换已偿还到期公司债券本金的自有资金，[21青信01]</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>华安证券股份有限公司,中国国际金融股份有限公司,东莞证券股份有限公司</t>
+          <t>中信证券股份有限公司,光大证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD48" s="3"/>
       <c r="AE48" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF48" s="3" t="inlineStr">
@@ -11293,7 +11289,7 @@
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>南京证券股份有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
+          <t>青岛国信发展(集团)有限责任公司2026年面向专业投资者公开发行公司债券(第七期)(品种二)</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
@@ -11303,13 +11299,17 @@
       </c>
       <c r="AJ48" s="3" t="inlineStr">
         <is>
-          <t>2028-10-26</t>
-        </is>
-      </c>
-      <c r="AK48" s="3"/>
+          <t>2036-10-26</t>
+        </is>
+      </c>
+      <c r="AK48" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL48" s="3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t/>
         </is>
       </c>
       <c r="AM48" s="3" t="inlineStr">
@@ -11324,32 +11324,32 @@
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP48" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ48" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT48" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU48" s="3" t="inlineStr">
@@ -11382,7 +11382,7 @@
     <row r="49" customHeight="true" ht="18.0">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>26国券S1</t>
+          <t>26宁证04</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -11392,64 +11392,64 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>245749.SH</t>
+          <t>246287.SH</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>0.55Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>50.0</v>
+        <v>20.0</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>1.00 ~ 2.00</t>
+          <t>1.20 ~ 2.00</t>
         </is>
       </c>
       <c r="H49" s="4" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>27.7</v>
+        <v>29.4</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>26国券K1</t>
+          <t>26宁证03</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>172D</t>
+          <t>1.92Y</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>1.3880</t>
+          <t>1.5380</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>1.4400/--</t>
+          <t>1.5700/--</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司</t>
+          <t>南京证券股份有限公司</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>B- 48.85</t>
+          <t>B- 35.34</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -11473,17 +11473,17 @@
         </is>
       </c>
       <c r="U49" s="4" t="n">
-        <v>4.345</v>
+        <v>4.64</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X49" s="3" t="inlineStr">
         <is>
-          <t>1.41%~1.45%</t>
+          <t>1.50%~1.60%</t>
         </is>
       </c>
       <c r="Y49" s="3" t="inlineStr">
@@ -11493,22 +11493,22 @@
       </c>
       <c r="Z49" s="3" t="inlineStr">
         <is>
-          <t>A-1</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="AA49" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB49" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于置换到期公司债券本金和补充流动资金。[安信证券股份有限公司2023年面向专业投资者公开发行公司债券(第一期)(品种一)]</t>
+          <t>本期债券募集资金不超过20亿元(含20亿元),全部用于偿还到期公司债券本金。[25宁证08]</t>
         </is>
       </c>
       <c r="AC49" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>华安证券股份有限公司,中国国际金融股份有限公司,东莞证券股份有限公司</t>
         </is>
       </c>
       <c r="AD49" s="3"/>
@@ -11519,7 +11519,7 @@
       </c>
       <c r="AF49" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG49" s="3" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="AH49" s="3" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司2026年面向专业投资者公开发行短期公司债券(第一期)</t>
+          <t>南京证券股份有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI49" s="3" t="inlineStr">
@@ -11539,13 +11539,13 @@
       </c>
       <c r="AJ49" s="3" t="inlineStr">
         <is>
-          <t>2027-05-14</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="AK49" s="3"/>
       <c r="AL49" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AM49" s="3" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="AP49" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ49" s="3" t="inlineStr">
@@ -11618,7 +11618,7 @@
     <row r="50" customHeight="true" ht="18.0">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>26苏高G1</t>
+          <t>26国券S1</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -11628,64 +11628,64 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>246253.SH</t>
+          <t>245749.SH</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.55Y</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>3.0</v>
+        <v>50.0</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>3.0</v>
+        <v>20.0</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.00 ~ 2.00</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>33.33</v>
+        <v>27.7</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>24苏高G3</t>
+          <t>26国券K1</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>1.06Y</t>
+          <t>172D</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1.5191</t>
+          <t>1.3880</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4400/--</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>苏州苏高新科技产业发展有限公司</t>
+          <t>国投证券股份有限公司</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>B- 37.78</t>
+          <t>B- 48.85</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -11709,53 +11709,53 @@
         </is>
       </c>
       <c r="U50" s="4" t="n">
-        <v>3.77</v>
+        <v>4.345</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X50" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.41%~1.45%</t>
         </is>
       </c>
       <c r="Y50" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z50" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>A-1</t>
+        </is>
+      </c>
       <c r="AA50" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB50" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将3.00亿元全部用于置换到期的公司债券本金。[23苏高G1]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于置换到期公司债券本金和补充流动资金。[安信证券股份有限公司2023年面向专业投资者公开发行公司债券(第一期)(品种一)]</t>
         </is>
       </c>
       <c r="AC50" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD50" s="3" t="inlineStr">
-        <is>
-          <t>苏州苏高新集团有限公司</t>
-        </is>
-      </c>
+          <t>国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD50" s="3"/>
       <c r="AE50" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF50" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG50" s="3" t="inlineStr">
@@ -11765,7 +11765,7 @@
       </c>
       <c r="AH50" s="3" t="inlineStr">
         <is>
-          <t>苏州苏高新科技产业发展有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>国投证券股份有限公司2026年面向专业投资者公开发行短期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI50" s="3" t="inlineStr">
@@ -11775,7 +11775,7 @@
       </c>
       <c r="AJ50" s="3" t="inlineStr">
         <is>
-          <t>2029-10-26</t>
+          <t>2027-05-14</t>
         </is>
       </c>
       <c r="AK50" s="3"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="AM50" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AN50" s="3" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP50" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ50" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT50" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU50" s="3" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="AV50" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW50" s="3" t="inlineStr">
@@ -11854,7 +11854,7 @@
     <row r="51" customHeight="true" ht="18.0">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>26民生G4</t>
+          <t>26苏高G1</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>246288.SH</t>
+          <t>246253.SH</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -11873,55 +11873,55 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>15.0</v>
+        <v>3.0</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>15.0</v>
+        <v>3.0</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>1.26</v>
+        <v>1.6</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>-0.67</v>
+        <v>33.33</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>26民生G2</t>
+          <t>24苏高G3</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>2.65Y</t>
+          <t>1.06Y</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>1.6291</t>
+          <t>1.5191</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>1.6400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>民生证券股份有限公司</t>
+          <t>苏州苏高新科技产业发展有限公司</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>C- 24.24</t>
+          <t>B- 37.78</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="U51" s="4" t="n">
-        <v>3.87</v>
+        <v>3.77</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="inlineStr">
@@ -11955,34 +11955,38 @@
       </c>
       <c r="X51" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y51" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z51" s="3"/>
       <c r="AA51" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB51" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将15.00亿元全部用于补充公司运营资金</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将3.00亿元全部用于置换到期的公司债券本金。[23苏高G1]</t>
         </is>
       </c>
       <c r="AC51" s="3" t="inlineStr">
         <is>
-          <t>国联民生证券承销保荐有限公司,华泰联合证券有限责任公司,国泰海通证券股份有限公司,中泰证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD51" s="3"/>
+          <t>东吴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr">
+        <is>
+          <t>苏州苏高新集团有限公司</t>
+        </is>
+      </c>
       <c r="AE51" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF51" s="3" t="inlineStr">
@@ -11997,7 +12001,7 @@
       </c>
       <c r="AH51" s="3" t="inlineStr">
         <is>
-          <t>民生证券股份有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
+          <t>苏州苏高新科技产业发展有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI51" s="3" t="inlineStr">
@@ -12018,7 +12022,7 @@
       </c>
       <c r="AM51" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AN51" s="3" t="inlineStr">
@@ -12028,32 +12032,32 @@
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP51" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ51" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT51" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU51" s="3" t="inlineStr">
@@ -12063,7 +12067,7 @@
       </c>
       <c r="AV51" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW51" s="3" t="inlineStr">
@@ -12086,7 +12090,7 @@
     <row r="52" customHeight="true" ht="18.0">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>华能YK36(取消发行)</t>
+          <t>26民生G4</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -12096,90 +12100,98 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>DY246271.SH</t>
+          <t>246288.SH</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>10+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F52" s="3"/>
+        <v>15.0</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>15.0</v>
+      </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>-0.67</v>
+      </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>26民生G2</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>2.65Y</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>1.6291</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>1.6400/--</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>民生证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>C- 24.24</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>10-22 15:00</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K52" s="3" t="inlineStr">
-        <is>
-          <t>华能YK21</t>
-        </is>
-      </c>
-      <c r="L52" s="3" t="inlineStr">
-        <is>
-          <t>9.01Y+N</t>
-        </is>
-      </c>
-      <c r="M52" s="3" t="inlineStr">
-        <is>
-          <t>1.9190</t>
-        </is>
-      </c>
-      <c r="N52" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>中国华能集团有限公司</t>
-        </is>
-      </c>
-      <c r="P52" s="3" t="inlineStr">
-        <is>
-          <t>B- 47.07</t>
-        </is>
-      </c>
-      <c r="Q52" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="R52" s="3" t="inlineStr">
-        <is>
-          <t>10-22 16:00</t>
-        </is>
-      </c>
-      <c r="S52" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T52" s="3" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="U52" s="3"/>
+      <c r="U52" s="4" t="n">
+        <v>3.87</v>
+      </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X52" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y52" s="3" t="inlineStr">
@@ -12187,35 +12199,31 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z52" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z52" s="3"/>
       <c r="AA52" s="3" t="inlineStr">
         <is>
-          <t>河北省-保定市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB52" s="3" t="inlineStr">
         <is>
-          <t>发行人前次公司债券募集资金与募集说明书披露的用途一致【华能YK33】</t>
+          <t>本期债券募集资金扣除发行费用后,拟将15.00亿元全部用于补充公司运营资金</t>
         </is>
       </c>
       <c r="AC52" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,招商证券股份有限公司,国投证券股份有限公司,兴业证券股份有限公司,长城证券股份有限公司,国开证券股份有限公司</t>
+          <t>国联民生证券承销保荐有限公司,华泰联合证券有限责任公司,国泰海通证券股份有限公司,中泰证券股份有限公司</t>
         </is>
       </c>
       <c r="AD52" s="3"/>
       <c r="AE52" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF52" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG52" s="3" t="inlineStr">
@@ -12225,7 +12233,7 @@
       </c>
       <c r="AH52" s="3" t="inlineStr">
         <is>
-          <t>中国华能集团有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第六期)(品种一)(取消发行)</t>
+          <t>民生证券股份有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI52" s="3" t="inlineStr">
@@ -12235,14 +12243,10 @@
       </c>
       <c r="AJ52" s="3" t="inlineStr">
         <is>
-          <t>2036-10-26</t>
-        </is>
-      </c>
-      <c r="AK52" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-26</t>
+        </is>
+      </c>
+      <c r="AK52" s="3"/>
       <c r="AL52" s="3" t="inlineStr">
         <is>
           <t/>
@@ -12250,7 +12254,7 @@
       </c>
       <c r="AM52" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AN52" s="3" t="inlineStr">
@@ -12260,32 +12264,32 @@
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP52" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ52" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT52" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU52" s="3" t="inlineStr">
@@ -12300,12 +12304,12 @@
       </c>
       <c r="AW52" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX52" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY52" s="3" t="inlineStr">
@@ -12318,7 +12322,7 @@
     <row r="53" customHeight="true" ht="18.0">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>26越资05</t>
+          <t>华能YK36(取消发行)</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -12328,49 +12332,43 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>525066.SZ</t>
+          <t>DY246271.SH</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>10+N</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F53" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F53" s="3"/>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>1.65 ~ 2.65</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="I53" s="4" t="n">
-        <v>48.86</v>
-      </c>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>26越秀资本MTN007</t>
+          <t>华能YK21</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>9.86Y</t>
+          <t>9.01Y+N</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>2.1770</t>
+          <t>1.9190</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -12380,12 +12378,12 @@
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>广州越秀资本控股集团股份有限公司</t>
+          <t>中国华能集团有限公司</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>C- 19.84</t>
+          <t>B- 47.07</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -12408,18 +12406,16 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="U53" s="4" t="n">
-        <v>3.92</v>
-      </c>
+      <c r="U53" s="3"/>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X53" s="3" t="inlineStr">
         <is>
-          <t>2.08%~2.18%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y53" s="3" t="inlineStr">
@@ -12434,17 +12430,17 @@
       </c>
       <c r="AA53" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>河北省-保定市</t>
         </is>
       </c>
       <c r="AB53" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券的募集资金扣除发行费用后拟用于偿还有息债务和补充流动资金,及适用的法律、法规允许的其他用途,具体用途将根据发行人资金需求情况确定。</t>
+          <t>发行人前次公司债券募集资金与募集说明书披露的用途一致【华能YK33】</t>
         </is>
       </c>
       <c r="AC53" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司,万联证券股份有限公司,兴业证券股份有限公司,广发证券股份有限公司</t>
+          <t>中信证券股份有限公司,招商证券股份有限公司,国投证券股份有限公司,兴业证券股份有限公司,长城证券股份有限公司,国开证券股份有限公司</t>
         </is>
       </c>
       <c r="AD53" s="3"/>
@@ -12455,17 +12451,17 @@
       </c>
       <c r="AF53" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG53" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH53" s="3" t="inlineStr">
         <is>
-          <t>广州越秀资本控股集团股份有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
+          <t>中国华能集团有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第六期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI53" s="3" t="inlineStr">
@@ -12500,32 +12496,32 @@
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP53" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ53" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AT53" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU53" s="3" t="inlineStr">
@@ -12540,12 +12536,12 @@
       </c>
       <c r="AW53" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX53" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY53" s="3" t="inlineStr">
@@ -12558,7 +12554,7 @@
     <row r="54" customHeight="true" ht="18.0">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>26力通K1(取消发行)</t>
+          <t>26越资05</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -12568,91 +12564,103 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>DY520534.SZ</t>
+          <t>525066.SZ</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F54" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
-        </is>
-      </c>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
+          <t>1.65 ~ 2.65</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>48.86</v>
+      </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>26越秀资本MTN007</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>9.86Y</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>2.1770</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>广州越秀资本控股集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>C- 19.84</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>10-22 16:00</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K54" s="3" t="inlineStr">
-        <is>
-          <t>26星乙V1</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="inlineStr">
-        <is>
-          <t>4.94Y</t>
-        </is>
-      </c>
-      <c r="M54" s="3" t="inlineStr">
-        <is>
-          <t>2.0864</t>
-        </is>
-      </c>
-      <c r="N54" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>辛集市力通科技有限公司</t>
-        </is>
-      </c>
-      <c r="P54" s="3" t="inlineStr">
-        <is>
-          <t>E 0.00</t>
-        </is>
-      </c>
-      <c r="Q54" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="R54" s="3" t="inlineStr">
-        <is>
-          <t>10-22 15:00</t>
-        </is>
-      </c>
-      <c r="S54" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T54" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="U54" s="3"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="U54" s="4" t="n">
+        <v>3.92</v>
+      </c>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X54" s="3"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>2.08%~2.18%</t>
+        </is>
+      </c>
       <c r="Y54" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z54" s="3" t="inlineStr">
@@ -12662,24 +12670,20 @@
       </c>
       <c r="AA54" s="3" t="inlineStr">
         <is>
-          <t>河北省-石家庄市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB54" s="3" t="inlineStr">
         <is>
-          <t>本次公司债券募集资金扣除发行费用后,拟用于设立或投向科技创新领域的基金出资</t>
+          <t>本期公司债券的募集资金扣除发行费用后拟用于偿还有息债务和补充流动资金,及适用的法律、法规允许的其他用途,具体用途将根据发行人资金需求情况确定。</t>
         </is>
       </c>
       <c r="AC54" s="3" t="inlineStr">
         <is>
-          <t>世纪证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD54" s="3" t="inlineStr">
-        <is>
-          <t>江西省信用融资担保集团股份有限公司</t>
-        </is>
-      </c>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司,万联证券股份有限公司,兴业证券股份有限公司,广发证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD54" s="3"/>
       <c r="AE54" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -12697,20 +12701,24 @@
       </c>
       <c r="AH54" s="3" t="inlineStr">
         <is>
-          <t>辛集市力通科技有限公司2026年面向专业投资者非公开发行科技创新公司债券(品种一)(取消发行)</t>
+          <t>广州越秀资本控股集团股份有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI54" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ54" s="3" t="inlineStr">
         <is>
-          <t>2031-10-23</t>
-        </is>
-      </c>
-      <c r="AK54" s="3"/>
+          <t>2036-10-26</t>
+        </is>
+      </c>
+      <c r="AK54" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL54" s="3" t="inlineStr">
         <is>
           <t/>
@@ -12723,33 +12731,37 @@
       </c>
       <c r="AN54" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP54" s="3"/>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
       <c r="AQ54" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT54" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU54" s="3" t="inlineStr">
@@ -12759,7 +12771,7 @@
       </c>
       <c r="AV54" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW54" s="3" t="inlineStr">
@@ -12782,7 +12794,7 @@
     <row r="55" customHeight="true" ht="18.0">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>26亦庄K8(取消发行)</t>
+          <t>26力通K1(取消发行)</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -12792,7 +12804,7 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>DY246269.SH</t>
+          <t>DY520534.SZ</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -12801,12 +12813,12 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>5.0</v>
+        <v>1.5</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H55" s="3"/>
@@ -12818,17 +12830,17 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>26亦庄K3</t>
+          <t>26星乙V1</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>4.75Y</t>
+          <t>4.94Y</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>1.6074</t>
+          <t>2.0864</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
@@ -12838,12 +12850,12 @@
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>北京亦庄国际投资发展有限公司</t>
+          <t>辛集市力通科技有限公司</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>C- 22.07</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -12853,7 +12865,7 @@
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>10-22 16:00</t>
+          <t>10-22 15:00</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr">
@@ -12863,47 +12875,47 @@
       </c>
       <c r="T55" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X55" s="3" t="inlineStr">
-        <is>
-          <t>1.63%~1.73%</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X55" s="3"/>
       <c r="Y55" s="3" t="inlineStr">
         <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z55" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
       <c r="AA55" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>河北省-石家庄市</t>
         </is>
       </c>
       <c r="AB55" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于生产性支出,包括偿还有息债务、补充流动资金等符合法律法规要求的用途。</t>
+          <t>本次公司债券募集资金扣除发行费用后,拟用于设立或投向科技创新领域的基金出资</t>
         </is>
       </c>
       <c r="AC55" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司,第一创业证券承销保荐有限责任公司,平安证券股份有限公司,中国国际金融股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD55" s="3"/>
+          <t>世纪证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr">
+        <is>
+          <t>江西省信用融资担保集团股份有限公司</t>
+        </is>
+      </c>
       <c r="AE55" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -12916,29 +12928,25 @@
       </c>
       <c r="AG55" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH55" s="3" t="inlineStr">
         <is>
-          <t>北京亦庄国际投资发展有限公司2026年面向专业投资者公开发行科技创新公司债券(第五期)(品种一)(取消发行)</t>
+          <t>辛集市力通科技有限公司2026年面向专业投资者非公开发行科技创新公司债券(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI55" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ55" s="3" t="inlineStr">
         <is>
-          <t>2031-10-26</t>
-        </is>
-      </c>
-      <c r="AK55" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-23</t>
+        </is>
+      </c>
+      <c r="AK55" s="3"/>
       <c r="AL55" s="3" t="inlineStr">
         <is>
           <t/>
@@ -12951,7 +12959,7 @@
       </c>
       <c r="AN55" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AO55" s="3" t="inlineStr">
@@ -12959,11 +12967,7 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP55" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AP55" s="3"/>
       <c r="AQ55" s="3" t="inlineStr">
         <is>
           <t>综合</t>
@@ -12971,12 +12975,12 @@
       </c>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT55" s="3" t="inlineStr">
@@ -12991,7 +12995,7 @@
       </c>
       <c r="AV55" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW55" s="3" t="inlineStr">
@@ -13014,7 +13018,7 @@
     <row r="56" customHeight="true" ht="18.0">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>26漳九08</t>
+          <t>26亦庄K8(取消发行)</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -13024,7 +13028,7 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>284218.SH</t>
+          <t>DY246269.SH</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -13033,30 +13037,24 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F56" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F56" s="3"/>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="I56" s="4" t="n">
-        <v>42.68</v>
-      </c>
+          <t>1.10 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>26漳九K3</t>
+          <t>26亦庄K3</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
@@ -13066,7 +13064,7 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>1.7761</t>
+          <t>1.6074</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
@@ -13076,12 +13074,12 @@
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>漳州市九龙江集团有限公司</t>
+          <t>北京亦庄国际投资发展有限公司</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>B- 40.45</t>
+          <t>C- 22.07</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -13104,18 +13102,16 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="U56" s="4" t="n">
-        <v>4.51</v>
-      </c>
+      <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X56" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y56" s="3" t="inlineStr">
@@ -13123,20 +13119,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z56" s="3"/>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA56" s="3" t="inlineStr">
         <is>
-          <t>福建省-漳州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB56" s="3" t="inlineStr">
         <is>
-          <t>本期债券拟使用10亿元募集资金偿还发行人到期有息债务[24龙溪4A,24龙溪4S]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于生产性支出,包括偿还有息债务、补充流动资金等符合法律法规要求的用途。</t>
         </is>
       </c>
       <c r="AC56" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司,第一创业证券承销保荐有限责任公司,平安证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD56" s="3"/>
@@ -13157,12 +13157,12 @@
       </c>
       <c r="AH56" s="3" t="inlineStr">
         <is>
-          <t>漳州市九龙江集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>北京亦庄国际投资发展有限公司2026年面向专业投资者公开发行科技创新公司债券(第五期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI56" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ56" s="3" t="inlineStr">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="AM56" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AN56" s="3" t="inlineStr">
@@ -13197,7 +13197,7 @@
       </c>
       <c r="AP56" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ56" s="3" t="inlineStr">
@@ -13207,17 +13207,17 @@
       </c>
       <c r="AR56" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS56" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT56" s="3" t="inlineStr">
         <is>
-          <t>医药商业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU56" s="3" t="inlineStr">
@@ -13250,7 +13250,7 @@
     <row r="57" customHeight="true" ht="18.0">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>26云港Y1(取消发行)</t>
+          <t>26漳九08</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -13260,43 +13260,49 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>DY284250.SH</t>
+          <t>284218.SH</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F57" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
+          <t>1.40 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>42.68</v>
+      </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>26云港02</t>
+          <t>26漳九K3</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>4.38Y</t>
+          <t>4.75Y</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>1.9506</t>
+          <t>1.7761</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
@@ -13306,12 +13312,12 @@
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>连云港港口集团有限公司</t>
+          <t>漳州市九龙江集团有限公司</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>C- 19.98</t>
+          <t>B- 40.45</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -13321,7 +13327,7 @@
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>10-22 15:00</t>
+          <t>10-22 16:00</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr">
@@ -13331,40 +13337,42 @@
       </c>
       <c r="T57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="U57" s="3"/>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="U57" s="4" t="n">
+        <v>4.51</v>
+      </c>
       <c r="V57" s="3"/>
       <c r="W57" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X57" s="3" t="inlineStr">
         <is>
-          <t>1.89%~1.99%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y57" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z57" s="3"/>
       <c r="AA57" s="3" t="inlineStr">
         <is>
-          <t>江苏省-连云港市</t>
+          <t>福建省-漳州市</t>
         </is>
       </c>
       <c r="AB57" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后，拟将5亿元全部用于偿还到期的公司债券本金【23 云港Y3】</t>
+          <t>本期债券拟使用10亿元募集资金偿还发行人到期有息债务[24龙溪4A,24龙溪4S]</t>
         </is>
       </c>
       <c r="AC57" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,东吴证券股份有限公司</t>
+          <t>平安证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD57" s="3"/>
@@ -13385,7 +13393,7 @@
       </c>
       <c r="AH57" s="3" t="inlineStr">
         <is>
-          <t>连云港港口集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)(取消发行)</t>
+          <t>漳州市九龙江集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI57" s="3" t="inlineStr">
@@ -13395,10 +13403,14 @@
       </c>
       <c r="AJ57" s="3" t="inlineStr">
         <is>
-          <t>2031-10-23</t>
-        </is>
-      </c>
-      <c r="AK57" s="3"/>
+          <t>2031-10-26</t>
+        </is>
+      </c>
+      <c r="AK57" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL57" s="3" t="inlineStr">
         <is>
           <t/>
@@ -13406,12 +13418,12 @@
       </c>
       <c r="AM57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AN57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AO57" s="3" t="inlineStr">
@@ -13421,27 +13433,27 @@
       </c>
       <c r="AP57" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ57" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT57" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>医药商业</t>
         </is>
       </c>
       <c r="AU57" s="3" t="inlineStr">
@@ -13456,7 +13468,7 @@
       </c>
       <c r="AW57" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX57" s="3" t="inlineStr">
@@ -13474,74 +13486,68 @@
     <row r="58" customHeight="true" ht="18.0">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>26闽高速SCP002</t>
+          <t>26云港Y1(取消发行)</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>10-22 18:00</t>
+          <t>10-22 19:00</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>012682521.IB</t>
+          <t>DY284250.SH</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="F58" s="4" t="n">
-        <v>7.0</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="F58" s="3"/>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="I58" s="4" t="n">
-        <v>21.72</v>
-      </c>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3"/>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>26闽高速SCP001</t>
+          <t>26云港02</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>268D</t>
+          <t>4.38Y</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1.4717</t>
+          <t>1.9506</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>1.4700/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>福建省高速公路集团有限公司</t>
+          <t>连云港港口集团有限公司</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>C- 19.98</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -13551,12 +13557,12 @@
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>10-22 09:00</t>
+          <t>10-22 15:00</t>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T58" s="3" t="inlineStr">
@@ -13564,45 +13570,43 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="U58" s="4" t="n">
-        <v>3.9857</v>
-      </c>
+      <c r="U58" s="3"/>
       <c r="V58" s="3"/>
       <c r="W58" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X58" s="3" t="inlineStr">
         <is>
-          <t>1.43%~1.47%</t>
+          <t>1.89%~1.99%</t>
         </is>
       </c>
       <c r="Y58" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z58" s="3"/>
       <c r="AA58" s="3" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>江苏省-连云港市</t>
         </is>
       </c>
       <c r="AB58" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券发行规模为人民币7亿元，用于偿还发行人到期债务</t>
+          <t>本期公司债券募集资金扣除发行费用后，拟将5亿元全部用于偿还到期的公司债券本金【23 云港Y3】</t>
         </is>
       </c>
       <c r="AC58" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司</t>
+          <t>国金证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD58" s="3"/>
       <c r="AE58" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF58" s="3" t="inlineStr">
@@ -13612,28 +13616,28 @@
       </c>
       <c r="AG58" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH58" s="3" t="inlineStr">
         <is>
-          <t>福建省高速公路集团有限公司2026年度第二期超短期融资券</t>
+          <t>连云港港口集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI58" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ58" s="3" t="inlineStr">
         <is>
-          <t>2027-07-20</t>
+          <t>2031-10-23</t>
         </is>
       </c>
       <c r="AK58" s="3"/>
       <c r="AL58" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t/>
         </is>
       </c>
       <c r="AM58" s="3" t="inlineStr">
@@ -13648,12 +13652,12 @@
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP58" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ58" s="3" t="inlineStr">
@@ -13663,17 +13667,17 @@
       </c>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AT58" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU58" s="3" t="inlineStr">
@@ -13688,7 +13692,7 @@
       </c>
       <c r="AW58" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX58" s="3" t="inlineStr">
@@ -13706,7 +13710,7 @@
     <row r="59" customHeight="true" ht="18.0">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>26中铁上投MTN002</t>
+          <t>26闽高速SCP002</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -13716,64 +13720,64 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>102684191.IB</t>
+          <t>012682521.IB</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>1.52 ~ 1.72</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>25.33</v>
+        <v>21.72</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>26中铁上投MTN001</t>
+          <t>26闽高速SCP001</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>2.61Y</t>
+          <t>268D</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>1.5914</t>
+          <t>1.4717</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>1.6100/--</t>
+          <t>1.4700/--</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>中铁(上海)投资集团有限公司</t>
+          <t>福建省高速公路集团有限公司</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>B 53.00</t>
+          <t>C 30.00</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -13788,7 +13792,7 @@
       </c>
       <c r="S59" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="T59" s="3" t="inlineStr">
@@ -13797,19 +13801,17 @@
         </is>
       </c>
       <c r="U59" s="4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V59" s="4" t="n">
-        <v>1.2</v>
-      </c>
+        <v>3.9857</v>
+      </c>
+      <c r="V59" s="3"/>
       <c r="W59" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X59" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>1.43%~1.47%</t>
         </is>
       </c>
       <c r="Y59" s="3" t="inlineStr">
@@ -13820,28 +13822,28 @@
       <c r="Z59" s="3"/>
       <c r="AA59" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="AB59" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行金额10亿元,拟用于公司本部及子公司偿还有息负债。</t>
+          <t>发行人本期超短期融资券发行规模为人民币7亿元，用于偿还发行人到期债务</t>
         </is>
       </c>
       <c r="AC59" s="3" t="inlineStr">
         <is>
-          <t>中国工商银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD59" s="3"/>
       <c r="AE59" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF59" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG59" s="3" t="inlineStr">
@@ -13851,7 +13853,7 @@
       </c>
       <c r="AH59" s="3" t="inlineStr">
         <is>
-          <t>中铁(上海)投资集团有限公司2026年度第二期中期票据</t>
+          <t>福建省高速公路集团有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI59" s="3" t="inlineStr">
@@ -13861,7 +13863,7 @@
       </c>
       <c r="AJ59" s="3" t="inlineStr">
         <is>
-          <t>2029-10-23</t>
+          <t>2027-07-20</t>
         </is>
       </c>
       <c r="AK59" s="3"/>
@@ -13882,32 +13884,32 @@
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP59" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ59" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT59" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU59" s="3" t="inlineStr">
@@ -13935,81 +13937,79 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="AZ59" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ59" s="3"/>
     </row>
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>26大龙01</t>
+          <t>26中铁上投MTN002</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>10-22 19:00</t>
+          <t>10-22 18:00</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>520528.SZ</t>
+          <t>102684191.IB</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.52 ~ 1.72</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>1.9</v>
+        <v>1.52</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>54.68</v>
+        <v>25.33</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>26空港03</t>
+          <t>26中铁上投MTN001</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>4.73Y</t>
+          <t>2.61Y</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>1.9162</t>
+          <t>1.5914</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>1.9300/--</t>
+          <t>1.6100/--</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>北京大龙控股有限公司</t>
+          <t>中铁(上海)投资集团有限公司</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>B 53.00</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -14019,12 +14019,12 @@
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>10-22 15:00</t>
+          <t>10-22 09:00</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="T60" s="3" t="inlineStr">
@@ -14033,15 +14033,21 @@
         </is>
       </c>
       <c r="U60" s="4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V60" s="3"/>
+        <v>2.8</v>
+      </c>
+      <c r="V60" s="4" t="n">
+        <v>1.2</v>
+      </c>
       <c r="W60" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X60" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>1.58%~1.68%</t>
+        </is>
+      </c>
       <c r="Y60" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -14050,97 +14056,101 @@
       <c r="Z60" s="3"/>
       <c r="AA60" s="3" t="inlineStr">
         <is>
-          <t>北京市-顺义区</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB60" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行总额不超过7亿元(含7亿元),募集资金扣除发行费用后拟将全部用于偿还有息债务</t>
+          <t>本期债务融资工具发行金额10亿元,拟用于公司本部及子公司偿还有息负债。</t>
         </is>
       </c>
       <c r="AC60" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司</t>
+          <t>中国工商银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD60" s="3"/>
       <c r="AE60" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF60" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG60" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH60" s="3" t="inlineStr">
         <is>
-          <t>北京大龙控股有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>中铁(上海)投资集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI60" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ60" s="3" t="inlineStr">
         <is>
-          <t>2031-10-23</t>
+          <t>2029-10-23</t>
         </is>
       </c>
       <c r="AK60" s="3"/>
       <c r="AL60" s="3" t="inlineStr">
         <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="AM60" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AN60" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AO60" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP60" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ60" s="3" t="inlineStr">
+        <is>
+          <t>建筑施工</t>
+        </is>
+      </c>
+      <c r="AR60" s="3" t="inlineStr">
+        <is>
+          <t>专业工程</t>
+        </is>
+      </c>
+      <c r="AS60" s="3" t="inlineStr">
+        <is>
+          <t>市政路桥</t>
+        </is>
+      </c>
+      <c r="AT60" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU60" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM60" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="AN60" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="AO60" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP60" s="3"/>
-      <c r="AQ60" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR60" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS60" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT60" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU60" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV60" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -14161,12 +14171,14 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="AZ60" s="3"/>
+      <c r="AZ60" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>26力通K2</t>
+          <t>26大龙01</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -14176,59 +14188,59 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>520535.SZ</t>
+          <t>520528.SZ</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1.5</v>
+        <v>7.0</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2.10 ~ 3.10</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>2.32</v>
+        <v>1.9</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>86.38</v>
+        <v>54.68</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>26垦利Z2</t>
+          <t>26空港03</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>6.92Y</t>
+          <t>4.73Y</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>2.3913</t>
+          <t>1.9162</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>--/2.3200</t>
+          <t>1.9300/--</t>
         </is>
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>辛集市力通科技有限公司</t>
+          <t>北京大龙控股有限公司</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
@@ -14257,45 +14269,37 @@
         </is>
       </c>
       <c r="U61" s="4" t="n">
-        <v>3.1667</v>
+        <v>2.1</v>
       </c>
       <c r="V61" s="3"/>
       <c r="W61" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X61" s="3"/>
       <c r="Y61" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z61" s="3" t="inlineStr">
-        <is>
           <t>AAA</t>
         </is>
       </c>
+      <c r="Z61" s="3"/>
       <c r="AA61" s="3" t="inlineStr">
         <is>
-          <t>河北省-石家庄市</t>
+          <t>北京市-顺义区</t>
         </is>
       </c>
       <c r="AB61" s="3" t="inlineStr">
         <is>
-          <t>本次公司债券募集资金扣除发行费用后,拟用于设立或投向科技创新领域的基金出资</t>
+          <t>本期债券发行总额不超过7亿元(含7亿元),募集资金扣除发行费用后拟将全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC61" s="3" t="inlineStr">
         <is>
-          <t>世纪证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD61" s="3" t="inlineStr">
-        <is>
-          <t>江西省信用融资担保集团股份有限公司</t>
-        </is>
-      </c>
+          <t>东方证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD61" s="3"/>
       <c r="AE61" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -14313,7 +14317,7 @@
       </c>
       <c r="AH61" s="3" t="inlineStr">
         <is>
-          <t>辛集市力通科技有限公司2026年面向专业投资者非公开发行科技创新公司债券(品种二)</t>
+          <t>北京大龙控股有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI61" s="3" t="inlineStr">
@@ -14323,14 +14327,10 @@
       </c>
       <c r="AJ61" s="3" t="inlineStr">
         <is>
-          <t>2033-10-23</t>
-        </is>
-      </c>
-      <c r="AK61" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-23</t>
+        </is>
+      </c>
+      <c r="AK61" s="3"/>
       <c r="AL61" s="3" t="inlineStr">
         <is>
           <t/>
@@ -14348,7 +14348,7 @@
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP61" s="3"/>
@@ -14379,7 +14379,7 @@
       </c>
       <c r="AV61" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW61" s="3" t="inlineStr">
@@ -14402,74 +14402,74 @@
     <row r="62" customHeight="true" ht="18.0">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>26中建投租SCP002</t>
+          <t>26力通K2</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>10-22 18:00</t>
+          <t>10-22 19:00</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>012682514.IB</t>
+          <t>520535.SZ</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>5.0</v>
+        <v>1.5</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>1.28 ~ 1.48</t>
+          <t>2.10 ~ 3.10</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>1.48</v>
+        <v>2.32</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>32.72</v>
+        <v>86.38</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>24建租02</t>
+          <t>26垦利Z2</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>297D</t>
+          <t>6.92Y</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>1.4778</t>
+          <t>2.3913</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.3200</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>中建投租赁股份有限公司</t>
+          <t>辛集市力通科技有限公司</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.16</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -14479,7 +14479,7 @@
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>10-22 09:00</t>
+          <t>10-22 15:00</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr">
@@ -14493,75 +14493,83 @@
         </is>
       </c>
       <c r="U62" s="4" t="n">
-        <v>0.32</v>
+        <v>3.1667</v>
       </c>
       <c r="V62" s="3"/>
       <c r="W62" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X62" s="3" t="inlineStr">
-        <is>
-          <t>1.50%~1.54%</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X62" s="3"/>
       <c r="Y62" s="3" t="inlineStr">
         <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z62" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z62" s="3"/>
       <c r="AA62" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>河北省-石家庄市</t>
         </is>
       </c>
       <c r="AB62" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行金额为5亿元,所募集资金用于偿还有息债务[26中建投租SCP001]</t>
+          <t>本次公司债券募集资金扣除发行费用后,拟用于设立或投向科技创新领域的基金出资</t>
         </is>
       </c>
       <c r="AC62" s="3" t="inlineStr">
         <is>
-          <t>北京银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD62" s="3"/>
+          <t>世纪证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD62" s="3" t="inlineStr">
+        <is>
+          <t>江西省信用融资担保集团股份有限公司</t>
+        </is>
+      </c>
       <c r="AE62" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF62" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG62" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH62" s="3" t="inlineStr">
         <is>
-          <t>中建投租赁股份有限公司2026年度第二期超短期融资券</t>
+          <t>辛集市力通科技有限公司2026年面向专业投资者非公开发行科技创新公司债券(品种二)</t>
         </is>
       </c>
       <c r="AI62" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ62" s="3" t="inlineStr">
         <is>
-          <t>2027-07-20</t>
-        </is>
-      </c>
-      <c r="AK62" s="3"/>
+          <t>2033-10-23</t>
+        </is>
+      </c>
+      <c r="AK62" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL62" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t/>
         </is>
       </c>
       <c r="AM62" s="3" t="inlineStr">
@@ -14576,32 +14584,28 @@
       </c>
       <c r="AO62" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP62" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP62" s="3"/>
       <c r="AQ62" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR62" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS62" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT62" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU62" s="3" t="inlineStr">
@@ -14611,7 +14615,7 @@
       </c>
       <c r="AV62" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW62" s="3" t="inlineStr">
@@ -14634,55 +14638,59 @@
     <row r="63" customHeight="true" ht="18.0">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>26长城证券CP011</t>
+          <t>26中建投租SCP002</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>10-22 17:00</t>
+          <t>10-22 18:00</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>072610205.IB</t>
+          <t>012682514.IB</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>0.41Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="G63" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>1.28 ~ 1.48</t>
+        </is>
+      </c>
       <c r="H63" s="4" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>27.52</v>
+        <v>32.72</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>26长城证券CP010</t>
+          <t>24建租02</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>127D</t>
+          <t>297D</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>1.4339</t>
+          <t>1.4778</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
@@ -14692,12 +14700,12 @@
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司</t>
+          <t>中建投租赁股份有限公司</t>
         </is>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.72</t>
+          <t>C+ 31.16</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
@@ -14720,16 +14728,18 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="U63" s="3"/>
+      <c r="U63" s="4" t="n">
+        <v>0.32</v>
+      </c>
       <c r="V63" s="3"/>
       <c r="W63" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X63" s="3" t="inlineStr">
         <is>
-          <t>1.44%~1.48%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y63" s="3" t="inlineStr">
@@ -14740,19 +14750,23 @@
       <c r="Z63" s="3"/>
       <c r="AA63" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
-        </is>
-      </c>
-      <c r="AB63" s="3"/>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="AB63" s="3" t="inlineStr">
+        <is>
+          <t>本期债务融资工具发行金额为5亿元,所募集资金用于偿还有息债务[26中建投租SCP001]</t>
+        </is>
+      </c>
       <c r="AC63" s="3" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司</t>
+          <t>北京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD63" s="3"/>
       <c r="AE63" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF63" s="3" t="inlineStr">
@@ -14767,7 +14781,7 @@
       </c>
       <c r="AH63" s="3" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司2026年度第十一期短期融资券</t>
+          <t>中建投租赁股份有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI63" s="3" t="inlineStr">
@@ -14777,7 +14791,7 @@
       </c>
       <c r="AJ63" s="3" t="inlineStr">
         <is>
-          <t>2027-03-23</t>
+          <t>2027-07-20</t>
         </is>
       </c>
       <c r="AK63" s="3"/>
@@ -14788,7 +14802,7 @@
       </c>
       <c r="AM63" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AN63" s="3" t="inlineStr">
@@ -14803,7 +14817,7 @@
       </c>
       <c r="AP63" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ63" s="3" t="inlineStr">
@@ -14813,17 +14827,17 @@
       </c>
       <c r="AR63" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS63" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT63" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU63" s="3" t="inlineStr">
@@ -14856,17 +14870,17 @@
     <row r="64" customHeight="true" ht="18.0">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>26陕建集团CP003</t>
+          <t>26长城证券CP011</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>10-22 18:00</t>
+          <t>10-22 17:00</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>042680354.IB</t>
+          <t>072610205.IB</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -14880,50 +14894,46 @@
       <c r="F64" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>2.60 ~ 5.60</t>
-        </is>
-      </c>
+      <c r="G64" s="3"/>
       <c r="H64" s="4" t="n">
-        <v>5.6</v>
+        <v>1.44</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>443.52</v>
+        <v>27.52</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>26陕建集团CP001</t>
+          <t>26长城证券CP010</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>143D</t>
+          <t>127D</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>5.5419</t>
+          <t>1.4339</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>6.5000/5.5400</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>陕西建工集团股份有限公司</t>
+          <t>长城证券股份有限公司</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>C 28.08</t>
+          <t>C+ 32.72</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -14946,18 +14956,16 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="U64" s="4" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="U64" s="3"/>
       <c r="V64" s="3"/>
       <c r="W64" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X64" s="3" t="inlineStr">
         <is>
-          <t>5.65%~5.69%</t>
+          <t>1.44%~1.48%</t>
         </is>
       </c>
       <c r="Y64" s="3" t="inlineStr">
@@ -14968,28 +14976,24 @@
       <c r="Z64" s="3"/>
       <c r="AA64" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
-        </is>
-      </c>
-      <c r="AB64" s="3" t="inlineStr">
-        <is>
-          <t>本期短期融资券采用发行金额动态调整机制,基础发行规模0亿元,发行金额上限10亿元,募集资金将全部用于偿还有息负债[26陕建集团SCP002(科创债)]</t>
-        </is>
-      </c>
+          <t>广东省-深圳市</t>
+        </is>
+      </c>
+      <c r="AB64" s="3"/>
       <c r="AC64" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>长城证券股份有限公司</t>
         </is>
       </c>
       <c r="AD64" s="3"/>
       <c r="AE64" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF64" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG64" s="3" t="inlineStr">
@@ -14999,7 +15003,7 @@
       </c>
       <c r="AH64" s="3" t="inlineStr">
         <is>
-          <t>陕西建工集团股份有限公司2026年度第三期短期融资券</t>
+          <t>长城证券股份有限公司2026年度第十一期短期融资券</t>
         </is>
       </c>
       <c r="AI64" s="3" t="inlineStr">
@@ -15009,7 +15013,7 @@
       </c>
       <c r="AJ64" s="3" t="inlineStr">
         <is>
-          <t>2027-03-22</t>
+          <t>2027-03-23</t>
         </is>
       </c>
       <c r="AK64" s="3"/>
@@ -15020,7 +15024,7 @@
       </c>
       <c r="AM64" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AN64" s="3" t="inlineStr">
@@ -15030,32 +15034,32 @@
       </c>
       <c r="AO64" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP64" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ64" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR64" s="3" t="inlineStr">
         <is>
-          <t>房屋建筑</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS64" s="3" t="inlineStr">
         <is>
-          <t>其他房建</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT64" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU64" s="3" t="inlineStr">
@@ -15088,135 +15092,135 @@
     <row r="65" customHeight="true" ht="18.0">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>26北金K1</t>
+          <t>26陕建集团CP003</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>10-22 19:00</t>
+          <t>10-22 18:00</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>284333.SH</t>
+          <t>042680354.IB</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>0.41Y</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>2.60 ~ 5.60</t>
         </is>
       </c>
       <c r="H65" s="4" t="n">
-        <v>1.65</v>
+        <v>5.6</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>29.68</v>
+        <v>443.52</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>5.54</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>26陕建集团CP001</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>143D</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>5.5419</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
+          <t>6.5000/5.5400</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>陕西建工集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>C 28.08</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="R65" s="3" t="inlineStr">
+        <is>
+          <t>10-22 09:00</t>
+        </is>
+      </c>
+      <c r="S65" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3"/>
-      <c r="M65" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N65" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O65" s="3" t="inlineStr">
-        <is>
-          <t>北京金控资本有限公司</t>
-        </is>
-      </c>
-      <c r="P65" s="3" t="inlineStr">
-        <is>
-          <t>E 0.00</t>
-        </is>
-      </c>
-      <c r="Q65" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="R65" s="3" t="inlineStr">
-        <is>
-          <t>10-22 15:00</t>
-        </is>
-      </c>
-      <c r="S65" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T65" s="3" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
       <c r="U65" s="4" t="n">
-        <v>6.625</v>
+        <v>0.2</v>
       </c>
       <c r="V65" s="3"/>
       <c r="W65" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X65" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>5.65%~5.69%</t>
         </is>
       </c>
       <c r="Y65" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z65" s="3" t="inlineStr">
-        <is>
           <t>AAA</t>
         </is>
       </c>
+      <c r="Z65" s="3"/>
       <c r="AA65" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB65" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券发行规模不超过4亿元,扣除发行费用后,拟用于基金出资和/或置换前12个月对基金出资</t>
+          <t>本期短期融资券采用发行金额动态调整机制,基础发行规模0亿元,发行金额上限10亿元,募集资金将全部用于偿还有息负债[26陕建集团SCP002(科创债)]</t>
         </is>
       </c>
       <c r="AC65" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD65" s="3" t="inlineStr">
-        <is>
-          <t>北京金融控股集团有限公司</t>
-        </is>
-      </c>
+          <t>平安银行股份有限公司,中国光大银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD65" s="3"/>
       <c r="AE65" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF65" s="3" t="inlineStr">
@@ -15226,79 +15230,83 @@
       </c>
       <c r="AG65" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH65" s="3" t="inlineStr">
         <is>
-          <t>北京金控资本有限公司2026年面向专业投资者非公开发行科技创新公司债券</t>
+          <t>陕西建工集团股份有限公司2026年度第三期短期融资券</t>
         </is>
       </c>
       <c r="AI65" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ65" s="3" t="inlineStr">
         <is>
-          <t>2031-10-23</t>
+          <t>2027-03-22</t>
         </is>
       </c>
       <c r="AK65" s="3"/>
       <c r="AL65" s="3" t="inlineStr">
         <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="AM65" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AN65" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AO65" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP65" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ65" s="3" t="inlineStr">
+        <is>
+          <t>建筑施工</t>
+        </is>
+      </c>
+      <c r="AR65" s="3" t="inlineStr">
+        <is>
+          <t>房屋建筑</t>
+        </is>
+      </c>
+      <c r="AS65" s="3" t="inlineStr">
+        <is>
+          <t>其他房建</t>
+        </is>
+      </c>
+      <c r="AT65" s="3" t="inlineStr">
+        <is>
+          <t>房屋建设</t>
+        </is>
+      </c>
+      <c r="AU65" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM65" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="AN65" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="AO65" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP65" s="3"/>
-      <c r="AQ65" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR65" s="3" t="inlineStr">
-        <is>
-          <t>其他非银</t>
-        </is>
-      </c>
-      <c r="AS65" s="3" t="inlineStr">
-        <is>
-          <t>其他非银</t>
-        </is>
-      </c>
-      <c r="AT65" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU65" s="3" t="inlineStr">
-        <is>
-          <t>2029-10-23</t>
-        </is>
-      </c>
       <c r="AV65" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW65" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX65" s="3" t="inlineStr">
@@ -15316,7 +15324,7 @@
     <row r="66" customHeight="true" ht="18.0">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>26穗交01</t>
+          <t>26北金K1</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -15326,64 +15334,56 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>525060.SZ</t>
+          <t>284333.SH</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>15.0</v>
+        <v>4.0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>15.0</v>
+        <v>4.0</v>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.00</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>30.68</v>
+        <v>29.68</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>26粤交投MTN008</t>
-        </is>
-      </c>
-      <c r="L66" s="3" t="inlineStr">
-        <is>
-          <t>4.84Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K66" s="3"/>
+      <c r="L66" s="3"/>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>1.6656</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>--/1.6600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>广州交通投资集团有限公司</t>
+          <t>北京金控资本有限公司</t>
         </is>
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.81</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -15407,45 +15407,49 @@
         </is>
       </c>
       <c r="U66" s="4" t="n">
-        <v>4.2867</v>
+        <v>6.625</v>
       </c>
       <c r="V66" s="3"/>
       <c r="W66" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X66" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y66" s="3" t="inlineStr">
         <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z66" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z66" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
       <c r="AA66" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB66" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将全部用于偿还到期的公司债券[21穗交04]</t>
+          <t>本期公司债券发行规模不超过4亿元,扣除发行费用后,拟用于基金出资和/或置换前12个月对基金出资</t>
         </is>
       </c>
       <c r="AC66" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD66" s="3"/>
+          <t>中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD66" s="3" t="inlineStr">
+        <is>
+          <t>北京金融控股集团有限公司</t>
+        </is>
+      </c>
       <c r="AE66" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -15458,17 +15462,17 @@
       </c>
       <c r="AG66" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH66" s="3" t="inlineStr">
         <is>
-          <t>广州交通投资集团有限公司2026年面向专业投资者公开发行公司债券</t>
+          <t>北京金控资本有限公司2026年面向专业投资者非公开发行科技创新公司债券</t>
         </is>
       </c>
       <c r="AI66" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ66" s="3" t="inlineStr">
@@ -15494,47 +15498,43 @@
       </c>
       <c r="AO66" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP66" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP66" s="3"/>
       <c r="AQ66" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR66" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS66" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT66" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU66" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-23</t>
         </is>
       </c>
       <c r="AV66" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW66" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX66" s="3" t="inlineStr">
@@ -15552,7 +15552,7 @@
     <row r="67" customHeight="true" ht="18.0">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>26交资本01</t>
+          <t>26穗交01</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -15562,64 +15562,64 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>520545.SZ</t>
+          <t>525060.SZ</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>3.0</v>
+        <v>15.0</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>3.0</v>
+        <v>15.0</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.30 ~ 2.00</t>
         </is>
       </c>
       <c r="H67" s="4" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>24.68</v>
+        <v>30.68</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>26交资K1</t>
+          <t>26粤交投MTN008</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>2.27Y+2.00Y</t>
+          <t>4.84Y</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>1.6237</t>
+          <t>1.6656</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>--/1.6100</t>
+          <t>--/1.6600</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>成都交投资本管理有限责任公司</t>
+          <t>广州交通投资集团有限公司</t>
         </is>
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.17</t>
+          <t>C+ 30.81</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -15643,41 +15643,45 @@
         </is>
       </c>
       <c r="U67" s="4" t="n">
-        <v>2.53</v>
+        <v>4.2867</v>
       </c>
       <c r="V67" s="3"/>
       <c r="W67" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X67" s="3"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X67" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
       <c r="Y67" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z67" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z67" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA67" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB67" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人有息债务</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将全部用于偿还到期的公司债券[21穗交04]</t>
         </is>
       </c>
       <c r="AC67" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD67" s="3" t="inlineStr">
-        <is>
-          <t>成都交通投资集团有限公司</t>
-        </is>
-      </c>
+          <t>平安证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD67" s="3"/>
       <c r="AE67" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -15695,12 +15699,12 @@
       </c>
       <c r="AH67" s="3" t="inlineStr">
         <is>
-          <t>成都交投资本管理有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>广州交通投资集团有限公司2026年面向专业投资者公开发行公司债券</t>
         </is>
       </c>
       <c r="AI67" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ67" s="3" t="inlineStr">
@@ -15726,43 +15730,47 @@
       </c>
       <c r="AO67" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP67" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP67" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
       <c r="AQ67" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR67" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS67" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT67" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU67" s="3" t="inlineStr">
         <is>
-          <t>2029-10-23</t>
+          <t/>
         </is>
       </c>
       <c r="AV67" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW67" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX67" s="3" t="inlineStr">
@@ -15780,74 +15788,74 @@
     <row r="68" customHeight="true" ht="18.0">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>26靖江农商行二级资本债01</t>
+          <t>26交资本01</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>10-22 18:00</t>
+          <t>10-22 19:00</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>232680048.IB</t>
+          <t>520545.SZ</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>2.19</v>
+        <v>1.6</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>54.86</v>
+        <v>24.68</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>26成泰农商行二级资本债01</t>
+          <t>26交资K1</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>4.93Y+5.00Y</t>
+          <t>2.27Y+2.00Y</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>2.3984</t>
+          <t>1.6237</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6100</t>
         </is>
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>江苏靖江农村商业银行股份有限公司</t>
+          <t>成都交投资本管理有限责任公司</t>
         </is>
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>C- 25.00</t>
+          <t>C+ 34.17</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -15857,7 +15865,7 @@
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>10-22 09:00</t>
+          <t>10-22 15:00</t>
         </is>
       </c>
       <c r="S68" s="3" t="inlineStr">
@@ -15870,83 +15878,81 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="U68" s="3"/>
+      <c r="U68" s="4" t="n">
+        <v>2.53</v>
+      </c>
       <c r="V68" s="3"/>
       <c r="W68" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="X68" s="3" t="inlineStr">
-        <is>
-          <t>2.34%~2.44%</t>
-        </is>
-      </c>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X68" s="3"/>
       <c r="Y68" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z68" s="3" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
+      <c r="Z68" s="3"/>
       <c r="AA68" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB68" s="3" t="inlineStr">
         <is>
-          <t>本次债券募集资金在扣除发行费用后,将依据适用法律和主管部门的批准用于补充发行人二级资本。</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还发行人有息债务</t>
         </is>
       </c>
       <c r="AC68" s="3" t="inlineStr">
         <is>
-          <t>申万宏源证券有限公司</t>
-        </is>
-      </c>
-      <c r="AD68" s="3"/>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD68" s="3" t="inlineStr">
+        <is>
+          <t>成都交通投资集团有限公司</t>
+        </is>
+      </c>
       <c r="AE68" s="3" t="inlineStr">
         <is>
-          <t>二级资本工具</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF68" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG68" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH68" s="3" t="inlineStr">
         <is>
-          <t>江苏靖江农村商业银行股份有限公司2026年二级资本债券</t>
+          <t>成都交投资本管理有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI68" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ68" s="3" t="inlineStr">
         <is>
-          <t>2036-10-23</t>
+          <t>2031-10-23</t>
         </is>
       </c>
       <c r="AK68" s="3"/>
       <c r="AL68" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t/>
         </is>
       </c>
       <c r="AM68" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AN68" s="3" t="inlineStr">
@@ -15959,39 +15965,35 @@
           <t>金融</t>
         </is>
       </c>
-      <c r="AP68" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+      <c r="AP68" s="3"/>
       <c r="AQ68" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR68" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS68" s="3" t="inlineStr">
         <is>
-          <t>农商行</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT68" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU68" s="3" t="inlineStr">
         <is>
-          <t>2031-10-23</t>
+          <t>2029-10-23</t>
         </is>
       </c>
       <c r="AV68" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW68" s="3" t="inlineStr">
@@ -16001,7 +16003,7 @@
       </c>
       <c r="AX68" s="3" t="inlineStr">
         <is>
-          <t>二级资本工具</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY68" s="3" t="inlineStr">
@@ -16014,7 +16016,7 @@
     <row r="69" customHeight="true" ht="18.0">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>26保利置业MTN004</t>
+          <t>26靖江农商行二级资本债01</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -16024,64 +16026,64 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>102684190.IB</t>
+          <t>232680048.IB</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>4.5</v>
+        <v>6.0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>5.5</v>
+        <v>6.0</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2.10 ~ 2.60</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H69" s="4" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>82.68</v>
+        <v>54.86</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>26保置04</t>
+          <t>26成泰农商行二级资本债01</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>4.92Y+2.00Y</t>
+          <t>4.93Y+5.00Y</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>2.3437</t>
+          <t>2.3984</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>2.3300/2.2982</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>保利置业集团有限公司</t>
+          <t>江苏靖江农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
-          <t>B- 35.72</t>
+          <t>C- 25.00</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr">
@@ -16104,52 +16106,52 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="U69" s="4" t="n">
-        <v>2.4545</v>
-      </c>
-      <c r="V69" s="4" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U69" s="3"/>
+      <c r="V69" s="3"/>
       <c r="W69" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X69" s="3" t="inlineStr">
         <is>
-          <t>2.46%~2.56%</t>
+          <t>2.34%~2.44%</t>
         </is>
       </c>
       <c r="Y69" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z69" s="3"/>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z69" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
       <c r="AA69" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB69" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模为5.50亿元,拟用于置换发行人偿还的债务融资工具本金及利息的自有资金[23保利置业MTN003,23保利置业MTN002]</t>
+          <t>本次债券募集资金在扣除发行费用后,将依据适用法律和主管部门的批准用于补充发行人二级资本。</t>
         </is>
       </c>
       <c r="AC69" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,宁波银行股份有限公司</t>
+          <t>申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD69" s="3"/>
       <c r="AE69" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>二级资本工具</t>
         </is>
       </c>
       <c r="AF69" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG69" s="3" t="inlineStr">
@@ -16159,7 +16161,7 @@
       </c>
       <c r="AH69" s="3" t="inlineStr">
         <is>
-          <t>保利置业集团有限公司2026年度第四期中期票据</t>
+          <t>江苏靖江农村商业银行股份有限公司2026年二级资本债券</t>
         </is>
       </c>
       <c r="AI69" s="3" t="inlineStr">
@@ -16169,7 +16171,7 @@
       </c>
       <c r="AJ69" s="3" t="inlineStr">
         <is>
-          <t>2031-10-23</t>
+          <t>2036-10-23</t>
         </is>
       </c>
       <c r="AK69" s="3"/>
@@ -16180,7 +16182,7 @@
       </c>
       <c r="AM69" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AN69" s="3" t="inlineStr">
@@ -16190,37 +16192,37 @@
       </c>
       <c r="AO69" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP69" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ69" s="3" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR69" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS69" s="3" t="inlineStr">
         <is>
-          <t>住宅楼房</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT69" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU69" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-10-23</t>
         </is>
       </c>
       <c r="AV69" s="3" t="inlineStr">
@@ -16230,12 +16232,12 @@
       </c>
       <c r="AW69" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX69" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>二级资本工具</t>
         </is>
       </c>
       <c r="AY69" s="3" t="inlineStr">
@@ -16248,70 +16250,74 @@
     <row r="70" customHeight="true" ht="18.0">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>26浙商银行债02</t>
+          <t>26保利置业MTN004</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>10-22 17:00</t>
+          <t>10-22 18:00</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>212680081.IB</t>
+          <t>102684190.IB</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>75.0</v>
+        <v>4.5</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>75.0</v>
-      </c>
-      <c r="G70" s="3"/>
+        <v>5.5</v>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>2.10 ~ 2.60</t>
+        </is>
+      </c>
       <c r="H70" s="4" t="n">
-        <v>1.55</v>
+        <v>2.18</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>28.33</v>
+        <v>82.68</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>26浙商银行债01</t>
+          <t>26保置04</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>2.99Y</t>
+          <t>4.92Y+2.00Y</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>1.5317</t>
+          <t>2.3437</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>1.5450/--</t>
+          <t>2.3300/2.2982</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司</t>
+          <t>保利置业集团有限公司</t>
         </is>
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>A 75.66</t>
+          <t>B- 35.72</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -16321,7 +16327,7 @@
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>10-22 09:30</t>
+          <t>10-22 09:00</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -16334,16 +16340,20 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="U70" s="3"/>
-      <c r="V70" s="3"/>
+      <c r="U70" s="4" t="n">
+        <v>2.4545</v>
+      </c>
+      <c r="V70" s="4" t="n">
+        <v>9.5</v>
+      </c>
       <c r="W70" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X70" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.60%</t>
+          <t>2.46%~2.56%</t>
         </is>
       </c>
       <c r="Y70" s="3" t="inlineStr">
@@ -16354,19 +16364,23 @@
       <c r="Z70" s="3"/>
       <c r="AA70" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB70" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
-        </is>
-      </c>
-      <c r="AC70" s="3"/>
+          <t>本期中期票据发行规模为5.50亿元,拟用于置换发行人偿还的债务融资工具本金及利息的自有资金[23保利置业MTN003,23保利置业MTN002]</t>
+        </is>
+      </c>
+      <c r="AC70" s="3" t="inlineStr">
+        <is>
+          <t>浙商银行股份有限公司,宁波银行股份有限公司</t>
+        </is>
+      </c>
       <c r="AD70" s="3"/>
       <c r="AE70" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF70" s="3" t="inlineStr">
@@ -16381,7 +16395,7 @@
       </c>
       <c r="AH70" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司2026年金融债券(第二期)</t>
+          <t>保利置业集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI70" s="3" t="inlineStr">
@@ -16391,7 +16405,7 @@
       </c>
       <c r="AJ70" s="3" t="inlineStr">
         <is>
-          <t>2029-10-23</t>
+          <t>2031-10-23</t>
         </is>
       </c>
       <c r="AK70" s="3"/>
@@ -16412,32 +16426,32 @@
       </c>
       <c r="AO70" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP70" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ70" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AR70" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AS70" s="3" t="inlineStr">
         <is>
-          <t>股份制银行</t>
+          <t>住宅楼房</t>
         </is>
       </c>
       <c r="AT70" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU70" s="3" t="inlineStr">
@@ -16470,74 +16484,70 @@
     <row r="71" customHeight="true" ht="18.0">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>26蓉金Y1</t>
+          <t>26浙商银行债02</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>10-22 19:00</t>
+          <t>10-22 17:00</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>246278.SH</t>
+          <t>212680081.IB</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>10.0</v>
+        <v>75.0</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
+        <v>75.0</v>
+      </c>
+      <c r="G71" s="3"/>
       <c r="H71" s="4" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>39.33</v>
+        <v>28.33</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>25蓉金Y1</t>
+          <t>26浙商银行债01</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>1.87Y+N</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>1.5522</t>
+          <t>1.5317</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
         <is>
-          <t>1.6200/--</t>
+          <t>1.5450/--</t>
         </is>
       </c>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>成都交子金融控股集团有限公司</t>
+          <t>浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>C 29.68</t>
+          <t>A 75.66</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -16547,7 +16557,7 @@
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>10-22 16:00</t>
+          <t>10-22 09:30</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr">
@@ -16560,18 +16570,16 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="U71" s="4" t="n">
-        <v>4.48</v>
-      </c>
+      <c r="U71" s="3"/>
       <c r="V71" s="3"/>
       <c r="W71" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X71" s="3" t="inlineStr">
         <is>
-          <t>1.62%~1.72%</t>
+          <t>1.50%~1.60%</t>
         </is>
       </c>
       <c r="Y71" s="3" t="inlineStr">
@@ -16582,38 +16590,34 @@
       <c r="Z71" s="3"/>
       <c r="AA71" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB71" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后，拟全部用于生产性支出，包括但不限于偿还到期有息债务等</t>
-        </is>
-      </c>
-      <c r="AC71" s="3" t="inlineStr">
-        <is>
-          <t>中信证券股份有限公司,华泰联合证券有限责任公司,广发证券股份有限公司,中泰证券股份有限公司</t>
-        </is>
-      </c>
+          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+        </is>
+      </c>
+      <c r="AC71" s="3"/>
       <c r="AD71" s="3"/>
       <c r="AE71" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF71" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG71" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH71" s="3" t="inlineStr">
         <is>
-          <t>成都交子金融控股集团有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
+          <t>浙商银行股份有限公司2026年金融债券(第二期)</t>
         </is>
       </c>
       <c r="AI71" s="3" t="inlineStr">
@@ -16629,7 +16633,7 @@
       <c r="AK71" s="3"/>
       <c r="AL71" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AM71" s="3" t="inlineStr">
@@ -16649,27 +16653,27 @@
       </c>
       <c r="AP71" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ71" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR71" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS71" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>股份制银行</t>
         </is>
       </c>
       <c r="AT71" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU71" s="3" t="inlineStr">
@@ -16684,7 +16688,7 @@
       </c>
       <c r="AW71" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX71" s="3" t="inlineStr">
@@ -16702,7 +16706,7 @@
     <row r="72" customHeight="true" ht="18.0">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>26东国03</t>
+          <t>26蓉金Y1</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -16712,64 +16716,64 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>284343.SH</t>
+          <t>246278.SH</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>14.7</v>
+        <v>10.0</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>14.7</v>
+        <v>10.0</v>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H72" s="4" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>36.33</v>
+        <v>39.33</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>26东国02</t>
+          <t>25蓉金Y1</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>2.98Y</t>
+          <t>1.87Y+N</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>1.6596</t>
+          <t>1.5522</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>1.8000/--</t>
+          <t>1.6200/--</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>北京市东城区国有资本运营有限公司</t>
+          <t>成都交子金融控股集团有限公司</t>
         </is>
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.75</t>
+          <t>C 29.68</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -16779,7 +16783,7 @@
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>10-22 15:00</t>
+          <t>10-22 16:00</t>
         </is>
       </c>
       <c r="S72" s="3" t="inlineStr">
@@ -16793,7 +16797,7 @@
         </is>
       </c>
       <c r="U72" s="4" t="n">
-        <v>3.5238</v>
+        <v>4.48</v>
       </c>
       <c r="V72" s="3"/>
       <c r="W72" s="3" t="inlineStr">
@@ -16803,7 +16807,7 @@
       </c>
       <c r="X72" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.62%~1.72%</t>
         </is>
       </c>
       <c r="Y72" s="3" t="inlineStr">
@@ -16814,17 +16818,17 @@
       <c r="Z72" s="3"/>
       <c r="AA72" s="3" t="inlineStr">
         <is>
-          <t>北京市-东城区</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB72" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后，全部用于偿还公司有息负债</t>
+          <t>本期公司债券募集资金扣除发行费用后，拟全部用于生产性支出，包括但不限于偿还到期有息债务等</t>
         </is>
       </c>
       <c r="AC72" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中邮证券有限责任公司,国新证券股份有限公司</t>
+          <t>中信证券股份有限公司,华泰联合证券有限责任公司,广发证券股份有限公司,中泰证券股份有限公司</t>
         </is>
       </c>
       <c r="AD72" s="3"/>
@@ -16845,12 +16849,12 @@
       </c>
       <c r="AH72" s="3" t="inlineStr">
         <is>
-          <t>北京市东城区国有资本运营有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>成都交子金融控股集团有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI72" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ72" s="3" t="inlineStr">
@@ -16876,32 +16880,32 @@
       </c>
       <c r="AO72" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP72" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ72" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR72" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS72" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT72" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU72" s="3" t="inlineStr">
@@ -16916,7 +16920,7 @@
       </c>
       <c r="AW72" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX72" s="3" t="inlineStr">
@@ -25624,7 +25628,7 @@
     <row r="110" customHeight="true" ht="18.0">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>26兖矿能源MTN003(并购)</t>
+          <t>26兖矿能源MTN003B(并购)(取消发行)</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -25634,54 +25638,48 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>102684213.IB</t>
+          <t>DY102684214.IB</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E110" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F110" s="4" t="n">
-        <v>20.0</v>
-      </c>
+      <c r="F110" s="3"/>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="I110" s="4" t="n">
-        <v>40.76</v>
-      </c>
+          <t>1.60 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H110" s="3"/>
+      <c r="I110" s="3"/>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>26兖矿能源MTN002A(并购)</t>
+          <t>26兖矿能源MTN002B(并购)</t>
         </is>
       </c>
       <c r="L110" s="3" t="inlineStr">
         <is>
-          <t>2.81Y+N</t>
+          <t>4.81Y+N</t>
         </is>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>1.6429</t>
+          <t>1.7789</t>
         </is>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8200/--</t>
         </is>
       </c>
       <c r="O110" s="3" t="inlineStr">
@@ -25714,12 +25712,8 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="U110" s="4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V110" s="4" t="n">
-        <v>4.0</v>
-      </c>
+      <c r="U110" s="3"/>
+      <c r="V110" s="3"/>
       <c r="W110" s="3" t="inlineStr">
         <is>
           <t>4+</t>
@@ -25727,7 +25721,7 @@
       </c>
       <c r="X110" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y110" s="3" t="inlineStr">
@@ -25773,7 +25767,7 @@
       </c>
       <c r="AH110" s="3" t="inlineStr">
         <is>
-          <t>兖矿能源集团股份有限公司2026年度第三期中期票据(并购)</t>
+          <t>兖矿能源集团股份有限公司2026年度第三期中期票据(并购)(品种二)(取消发行)</t>
         </is>
       </c>
       <c r="AI110" s="3" t="inlineStr">
@@ -25783,10 +25777,14 @@
       </c>
       <c r="AJ110" s="3" t="inlineStr">
         <is>
-          <t>2029-10-26</t>
-        </is>
-      </c>
-      <c r="AK110" s="3"/>
+          <t>2031-10-26</t>
+        </is>
+      </c>
+      <c r="AK110" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL110" s="3" t="inlineStr">
         <is>
           <t>2026-10-27</t>
@@ -25844,7 +25842,7 @@
       </c>
       <c r="AW110" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX110" s="3" t="inlineStr">
@@ -25862,68 +25860,74 @@
     <row r="111" customHeight="true" ht="18.0">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>26兖矿能源MTN003B(并购)(取消发行)</t>
+          <t>26桓台金海PPN001</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>10-23 18:00</t>
+          <t>10-22 18:00</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>DY102684214.IB</t>
+          <t>032680596.IB</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E111" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F111" s="3"/>
+      <c r="F111" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H111" s="3"/>
-      <c r="I111" s="3"/>
+          <t>1.90 ~ 2.90</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="I111" s="4" t="n">
+        <v>93.68</v>
+      </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>26兖矿能源MTN002B(并购)</t>
+          <t>25桓台01</t>
         </is>
       </c>
       <c r="L111" s="3" t="inlineStr">
         <is>
-          <t>4.81Y+N</t>
+          <t>3.87Y</t>
         </is>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
-          <t>1.7789</t>
+          <t>2.1121</t>
         </is>
       </c>
       <c r="N111" s="3" t="inlineStr">
         <is>
-          <t>1.8200/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O111" s="3" t="inlineStr">
         <is>
-          <t>兖矿能源集团股份有限公司</t>
+          <t>桓台县金海公有资产经营有限公司</t>
         </is>
       </c>
       <c r="P111" s="3" t="inlineStr">
         <is>
-          <t>B- 40.60</t>
+          <t>B- 37.63</t>
         </is>
       </c>
       <c r="Q111" s="3" t="inlineStr">
@@ -25933,7 +25937,7 @@
       </c>
       <c r="R111" s="3" t="inlineStr">
         <is>
-          <t>10-22 10:00</t>
+          <t>10-22 14:00</t>
         </is>
       </c>
       <c r="S111" s="3" t="inlineStr">
@@ -25943,50 +25947,48 @@
       </c>
       <c r="T111" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="U111" s="3"/>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="U111" s="4" t="n">
+        <v>2.37</v>
+      </c>
       <c r="V111" s="3"/>
       <c r="W111" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X111" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>2.07%~2.17%</t>
         </is>
       </c>
       <c r="Y111" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z111" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z111" s="3"/>
       <c r="AA111" s="3" t="inlineStr">
         <is>
-          <t>山东省-济宁市</t>
+          <t>山东省-淄博市</t>
         </is>
       </c>
       <c r="AB111" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模上限25亿元,拟用于置换发行人一年内归还并购贷款的自有资金</t>
+          <t>本期定向债务融资工具拟发行10.00亿元,拟全部用于偿还“23桓台金海PPN001”回售资金[23桓台金海PPN001]</t>
         </is>
       </c>
       <c r="AC111" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,招商银行股份有限公司,中国银行股份有限公司</t>
+          <t>长城证券股份有限公司,中泰证券股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD111" s="3"/>
       <c r="AE111" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF111" s="3" t="inlineStr">
@@ -26001,27 +26003,23 @@
       </c>
       <c r="AH111" s="3" t="inlineStr">
         <is>
-          <t>兖矿能源集团股份有限公司2026年度第三期中期票据(并购)(品种二)(取消发行)</t>
+          <t>桓台县金海公有资产经营有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI111" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ111" s="3" t="inlineStr">
         <is>
-          <t>2031-10-26</t>
-        </is>
-      </c>
-      <c r="AK111" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-23</t>
+        </is>
+      </c>
+      <c r="AK111" s="3"/>
       <c r="AL111" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="AM111" s="3" t="inlineStr">
@@ -26031,37 +26029,37 @@
       </c>
       <c r="AN111" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AO111" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP111" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ111" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR111" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS111" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT111" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU111" s="3" t="inlineStr">
@@ -26076,17 +26074,17 @@
       </c>
       <c r="AW111" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX111" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY111" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AZ111" s="3"/>
@@ -26094,7 +26092,7 @@
     <row r="112" customHeight="true" ht="18.0">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>26桓台金海PPN001</t>
+          <t>26悦达PPN003A</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -26104,7 +26102,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>032680596.IB</t>
+          <t>032680598.IB</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
@@ -26113,55 +26111,55 @@
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H112" s="4" t="n">
-        <v>2.29</v>
+        <v>2.0</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>93.68</v>
+        <v>64.68</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>25桓台01</t>
+          <t>26悦达PPN002</t>
         </is>
       </c>
       <c r="L112" s="3" t="inlineStr">
         <is>
-          <t>3.87Y</t>
+          <t>4.87Y</t>
         </is>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>2.1121</t>
+          <t>2.0483</t>
         </is>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9700/1.9500</t>
         </is>
       </c>
       <c r="O112" s="3" t="inlineStr">
         <is>
-          <t>桓台县金海公有资产经营有限公司</t>
+          <t>江苏悦达集团有限公司</t>
         </is>
       </c>
       <c r="P112" s="3" t="inlineStr">
         <is>
-          <t>B- 37.63</t>
+          <t>C- 23.57</t>
         </is>
       </c>
       <c r="Q112" s="3" t="inlineStr">
@@ -26171,12 +26169,12 @@
       </c>
       <c r="R112" s="3" t="inlineStr">
         <is>
-          <t>10-22 14:00</t>
+          <t>10-22 09:00</t>
         </is>
       </c>
       <c r="S112" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T112" s="3" t="inlineStr">
@@ -26185,38 +26183,40 @@
         </is>
       </c>
       <c r="U112" s="4" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="V112" s="3"/>
+        <v>3.2333</v>
+      </c>
+      <c r="V112" s="4" t="n">
+        <v>1.83</v>
+      </c>
       <c r="W112" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X112" s="3" t="inlineStr">
         <is>
-          <t>2.07%~2.17%</t>
+          <t>2.47%~2.57%</t>
         </is>
       </c>
       <c r="Y112" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z112" s="3"/>
       <c r="AA112" s="3" t="inlineStr">
         <is>
-          <t>山东省-淄博市</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="AB112" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具拟发行10.00亿元,拟全部用于偿还“23桓台金海PPN001”回售资金[23桓台金海PPN001]</t>
+          <t>本期定向债务融资工具发行规模为5亿元，拟全部用于偿还公司有息债务本息[24悦达MTN005]</t>
         </is>
       </c>
       <c r="AC112" s="3" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司,中泰证券股份有限公司,光大证券股份有限公司</t>
+          <t>南京银行股份有限公司,中信建投证券股份有限公司,招商证券股份有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD112" s="3"/>
@@ -26237,7 +26237,7 @@
       </c>
       <c r="AH112" s="3" t="inlineStr">
         <is>
-          <t>桓台县金海公有资产经营有限公司2026年度第一期定向债务融资工具</t>
+          <t>江苏悦达集团有限公司2026年度第三期定向债务融资工具(品种一)</t>
         </is>
       </c>
       <c r="AI112" s="3" t="inlineStr">
@@ -26268,32 +26268,32 @@
       </c>
       <c r="AO112" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP112" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ112" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR112" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS112" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT112" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU112" s="3" t="inlineStr">
@@ -26321,12 +26321,14 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="AZ112" s="3"/>
+      <c r="AZ112" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="113" customHeight="true" ht="18.0">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>26悦达PPN003A</t>
+          <t>26悦达PPN003B</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -26336,34 +26338,34 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>032680598.IB</t>
+          <t>032680599.IB</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H113" s="4" t="n">
-        <v>2.0</v>
+        <v>2.28</v>
       </c>
       <c r="I113" s="4" t="n">
-        <v>64.68</v>
+        <v>82.38</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K113" s="3" t="inlineStr">
@@ -26408,7 +26410,7 @@
       </c>
       <c r="S113" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="T113" s="3" t="inlineStr">
@@ -26417,10 +26419,10 @@
         </is>
       </c>
       <c r="U113" s="4" t="n">
-        <v>3.2333</v>
+        <v>3.7</v>
       </c>
       <c r="V113" s="4" t="n">
-        <v>1.83</v>
+        <v>7.0</v>
       </c>
       <c r="W113" s="3" t="inlineStr">
         <is>
@@ -26429,7 +26431,7 @@
       </c>
       <c r="X113" s="3" t="inlineStr">
         <is>
-          <t>2.47%~2.57%</t>
+          <t>2.87%~2.97%</t>
         </is>
       </c>
       <c r="Y113" s="3" t="inlineStr">
@@ -26471,7 +26473,7 @@
       </c>
       <c r="AH113" s="3" t="inlineStr">
         <is>
-          <t>江苏悦达集团有限公司2026年度第三期定向债务融资工具(品种一)</t>
+          <t>江苏悦达集团有限公司2026年度第三期定向债务融资工具(品种二)</t>
         </is>
       </c>
       <c r="AI113" s="3" t="inlineStr">
@@ -26481,10 +26483,14 @@
       </c>
       <c r="AJ113" s="3" t="inlineStr">
         <is>
-          <t>2031-10-23</t>
-        </is>
-      </c>
-      <c r="AK113" s="3"/>
+          <t>2033-10-23</t>
+        </is>
+      </c>
+      <c r="AK113" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL113" s="3" t="inlineStr">
         <is>
           <t>2026-10-26</t>
@@ -26562,74 +26568,74 @@
     <row r="114" customHeight="true" ht="18.0">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>26悦达PPN003B</t>
+          <t>26云港Y2</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>10-22 18:00</t>
+          <t>10-22 19:00</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>032680599.IB</t>
+          <t>284251.SH</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>7+N</t>
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>2.0</v>
+        <v>2.5</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H114" s="4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I114" s="4" t="n">
-        <v>82.38</v>
+        <v>84.38</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>26悦达PPN002</t>
+          <t>25云港Y4</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr">
         <is>
-          <t>4.87Y</t>
+          <t>3.89Y+N</t>
         </is>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>2.0483</t>
+          <t>1.9177</t>
         </is>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
-          <t>1.9700/1.9500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O114" s="3" t="inlineStr">
         <is>
-          <t>江苏悦达集团有限公司</t>
+          <t>连云港港口集团有限公司</t>
         </is>
       </c>
       <c r="P114" s="3" t="inlineStr">
         <is>
-          <t>C- 23.57</t>
+          <t>C- 19.98</t>
         </is>
       </c>
       <c r="Q114" s="3" t="inlineStr">
@@ -26639,12 +26645,12 @@
       </c>
       <c r="R114" s="3" t="inlineStr">
         <is>
-          <t>10-22 09:00</t>
+          <t>10-22 15:00</t>
         </is>
       </c>
       <c r="S114" s="3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T114" s="3" t="inlineStr">
@@ -26653,46 +26659,44 @@
         </is>
       </c>
       <c r="U114" s="4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="V114" s="4" t="n">
-        <v>7.0</v>
-      </c>
+        <v>3.44</v>
+      </c>
+      <c r="V114" s="3"/>
       <c r="W114" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X114" s="3" t="inlineStr">
         <is>
-          <t>2.87%~2.97%</t>
+          <t>2.14%~2.24%</t>
         </is>
       </c>
       <c r="Y114" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z114" s="3"/>
       <c r="AA114" s="3" t="inlineStr">
         <is>
-          <t>江苏省-盐城市</t>
+          <t>江苏省-连云港市</t>
         </is>
       </c>
       <c r="AB114" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行规模为5亿元，拟全部用于偿还公司有息债务本息[24悦达MTN005]</t>
+          <t>本期公司债券募集资金扣除发行费用后，拟将5亿元全部用于偿还到期的公司债券本金【23 云港Y3】</t>
         </is>
       </c>
       <c r="AC114" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,中信建投证券股份有限公司,招商证券股份有限公司,东吴证券股份有限公司</t>
+          <t>国金证券股份有限公司,中信证券股份有限公司,国泰海通证券股份有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD114" s="3"/>
       <c r="AE114" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF114" s="3" t="inlineStr">
@@ -26702,12 +26706,12 @@
       </c>
       <c r="AG114" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH114" s="3" t="inlineStr">
         <is>
-          <t>江苏悦达集团有限公司2026年度第三期定向债务融资工具(品种二)</t>
+          <t>连云港港口集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI114" s="3" t="inlineStr">
@@ -26727,7 +26731,7 @@
       </c>
       <c r="AL114" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AM114" s="3" t="inlineStr">
@@ -26747,27 +26751,27 @@
       </c>
       <c r="AP114" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ114" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR114" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AS114" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AT114" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU114" s="3" t="inlineStr">
@@ -26782,7 +26786,7 @@
       </c>
       <c r="AW114" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX114" s="3" t="inlineStr">
@@ -26795,9 +26799,7 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="AZ114" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ114" s="3"/>
     </row>
   </sheetData>
   <mergeCells>
